--- a/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,2186 +425,2912 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P32"/>
+  <dimension ref="A1:P42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>team_home</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>team_away</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>country</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>competition</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>referee</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>venue</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>capacity</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>attendance</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>id_team_home</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>team_home</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>id_team_away</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>team_away</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>id_country</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_competition</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>is_cup</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>season</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
+          <t>zuzbQnCF</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>23.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Borussia-Park
+ (Mönchengladbach)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>54 042</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>59</v>
+      </c>
+      <c r="L2" t="n">
+        <v>591</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>YZZcMwBs</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>24.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>WWK Arena
+ (Augsburg)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>30 660</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>59</v>
+      </c>
+      <c r="L3" t="n">
+        <v>591</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>GbeXvnR8</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>24.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Europa-Park Stadion
+ (Freiburg)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>34 700</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>59</v>
+      </c>
+      <c r="L4" t="n">
+        <v>591</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>O48oHrZ1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>24.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PreZero Arena
+ (Sinsheim)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>30 150</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>59</v>
+      </c>
+      <c r="L5" t="n">
+        <v>591</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2FREIeA6</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>24.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Mewa Arena
+ (Mainz)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>34 000</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>59</v>
+      </c>
+      <c r="L6" t="n">
+        <v>591</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>dfO6OQtS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>24.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Red Bull Arena
+ (Leipzig)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>47 069</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>59</v>
+      </c>
+      <c r="L7" t="n">
+        <v>591</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>SxFxJ44k</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>24.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Signal Iduna Park
+ (Dortmund)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>81 365</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>59</v>
+      </c>
+      <c r="L8" t="n">
+        <v>591</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>t0w6KHuf</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>25.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Volkswagen Arena
+ (Wolfsburg)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>28 917</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>59</v>
+      </c>
+      <c r="L9" t="n">
+        <v>591</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AuVMGZvJ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>25.08.2024 12:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Millerntor-Stadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>29 546</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>59</v>
+      </c>
+      <c r="L10" t="n">
+        <v>591</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
           <t>pWQQJq6l</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>16.08.2024 13:00</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
         <is>
           <t>Leuna Chemie Stadion
  (Halle)</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>15 057</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
         <is>
           <t>boX3cIQa</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Hallescher</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>ILyJuN3g</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>St. Pauli</t>
         </is>
       </c>
-      <c r="M2" t="n">
-        <v>59</v>
-      </c>
-      <c r="N2" t="n">
+      <c r="K11" t="n">
+        <v>59</v>
+      </c>
+      <c r="L11" t="n">
         <v>593</v>
       </c>
-      <c r="O2" t="n">
+      <c r="M11" t="n">
         <v>1</v>
       </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>hIsO3XFj</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>16.08.2024 13:00</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
         <is>
           <t>BRITA-Arena
  (Wiesbaden)</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>12 566</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
         <is>
           <t>ObxFt3lm</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Wehen</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>EuakNmc1</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Mainz</t>
         </is>
       </c>
-      <c r="M3" t="n">
-        <v>59</v>
-      </c>
-      <c r="N3" t="n">
+      <c r="K12" t="n">
+        <v>59</v>
+      </c>
+      <c r="L12" t="n">
         <v>593</v>
       </c>
-      <c r="O3" t="n">
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>EF8gXauC</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>16.08.2024 13:00</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Flyeralarm Arena
  (Wurzburger)</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>13 090</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
         <is>
           <t>nVM1YUFj</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Wurzburger Kickers</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>hQAtP9Sl</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Hoffenheim</t>
         </is>
       </c>
-      <c r="M4" t="n">
-        <v>59</v>
-      </c>
-      <c r="N4" t="n">
+      <c r="K13" t="n">
+        <v>59</v>
+      </c>
+      <c r="L13" t="n">
         <v>593</v>
       </c>
-      <c r="O4" t="n">
+      <c r="M13" t="n">
         <v>1</v>
       </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>lONsG15D</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>16.08.2024 15:45</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Donaustadion
  (Ulm)</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>19 500</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>tbC3EcQn</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Ulm</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>nVp0wiqd</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Bayern Munich</t>
         </is>
       </c>
-      <c r="M5" t="n">
-        <v>59</v>
-      </c>
-      <c r="N5" t="n">
+      <c r="K14" t="n">
+        <v>59</v>
+      </c>
+      <c r="L14" t="n">
         <v>593</v>
       </c>
-      <c r="O5" t="n">
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>0K2qBFNG</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>17.08.2024 08:00</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Erzgebirgsstadion
  (Aue)</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>16 485</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
         <is>
           <t>vsXIDreP</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Aue</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>88HSzjDr</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>B. Monchengladbach</t>
         </is>
       </c>
-      <c r="M6" t="n">
-        <v>59</v>
-      </c>
-      <c r="N6" t="n">
+      <c r="K15" t="n">
+        <v>59</v>
+      </c>
+      <c r="L15" t="n">
         <v>593</v>
       </c>
-      <c r="O6" t="n">
+      <c r="M15" t="n">
         <v>1</v>
       </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Kj4sifWp</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>17.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Bruchwegstadion
+ (Mainz)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>7 134</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>WzEYqEyg</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Schott Mainz</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>CCQGbik8</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Greuther Furth</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>59</v>
+      </c>
+      <c r="L16" t="n">
+        <v>593</v>
+      </c>
+      <c r="M16" t="n">
+        <v>1</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>17.08.2024 08:00</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>WzEYqEyg</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Schott Mainz</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>CCQGbik8</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>Greuther Furth</t>
-        </is>
-      </c>
-      <c r="M7" t="n">
-        <v>59</v>
-      </c>
-      <c r="N7" t="n">
-        <v>593</v>
-      </c>
-      <c r="O7" t="n">
-        <v>1</v>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>bF2q76Mr</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>17.08.2024 10:30</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
         <is>
           <t>OSTALB ARENA
  (Aalen)</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>14 500</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
         <is>
           <t>Oh2C15j0</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Aalen</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>0Ija0Ej9</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Schalke</t>
         </is>
       </c>
-      <c r="M8" t="n">
-        <v>59</v>
-      </c>
-      <c r="N8" t="n">
+      <c r="K17" t="n">
+        <v>59</v>
+      </c>
+      <c r="L17" t="n">
         <v>593</v>
       </c>
-      <c r="O8" t="n">
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>vyk5gjdE</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>17.08.2024 10:30</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Volksstadion Greifswald
  (Greifswald)</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>4 990</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
         <is>
           <t>Q1yNyI5t</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Greifswald</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>pzHW4oaE</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Union Berlin</t>
         </is>
       </c>
-      <c r="M9" t="n">
-        <v>59</v>
-      </c>
-      <c r="N9" t="n">
+      <c r="K18" t="n">
+        <v>59</v>
+      </c>
+      <c r="L18" t="n">
         <v>593</v>
       </c>
-      <c r="O9" t="n">
+      <c r="M18" t="n">
         <v>1</v>
       </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>tbKZHNz1</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>17.08.2024 10:30</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
         <is>
           <t>Audi Sportpark
  (Ingolstadt)</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>15 800</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
         <is>
           <t>ne5QkLtB</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Ingolstadt</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>naWckLmC</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Kaiserslautern</t>
         </is>
       </c>
-      <c r="M10" t="n">
-        <v>59</v>
-      </c>
-      <c r="N10" t="n">
+      <c r="K19" t="n">
+        <v>59</v>
+      </c>
+      <c r="L19" t="n">
         <v>593</v>
       </c>
-      <c r="O10" t="n">
+      <c r="M19" t="n">
         <v>1</v>
       </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>MZjh9ghT</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>17.08.2024 10:30</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
         <is>
           <t>Stadion an der Hafenstrasse
  (Essen)</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>20 352</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr">
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
         <is>
           <t>EB0xsr77</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>RW Essen</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>KbS1suSm</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>RB Leipzig</t>
         </is>
       </c>
-      <c r="M11" t="n">
-        <v>59</v>
-      </c>
-      <c r="N11" t="n">
+      <c r="K20" t="n">
+        <v>59</v>
+      </c>
+      <c r="L20" t="n">
         <v>593</v>
       </c>
-      <c r="O11" t="n">
+      <c r="M20" t="n">
         <v>1</v>
       </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>f1nnRRDE</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>17.08.2024 10:30</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Stadion an der Bremer Brück
  (Osnabrück)</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>16 667</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr">
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
         <is>
           <t>88Xgj1Y5</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>VfL Osnabruck</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>fiEQZ7C7</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Freiburg</t>
         </is>
       </c>
-      <c r="M12" t="n">
-        <v>59</v>
-      </c>
-      <c r="N12" t="n">
+      <c r="K21" t="n">
+        <v>59</v>
+      </c>
+      <c r="L21" t="n">
         <v>593</v>
       </c>
-      <c r="O12" t="n">
+      <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>8QPARz8c</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>17.08.2024 10:30</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
         <is>
           <t>MS Technologie Arena
  (Villingen-Schwenningen)</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>8 000</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr">
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
         <is>
           <t>lKLJUxeT</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Villingen</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>KWixEVWi</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Heidenheim</t>
         </is>
       </c>
-      <c r="M13" t="n">
-        <v>59</v>
-      </c>
-      <c r="N13" t="n">
+      <c r="K22" t="n">
+        <v>59</v>
+      </c>
+      <c r="L22" t="n">
         <v>593</v>
       </c>
-      <c r="O13" t="n">
+      <c r="M22" t="n">
         <v>1</v>
       </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>hzyf0b9b</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>17.08.2024 13:00</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
         <is>
           <t>New Tivoli
  (Aachen)</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>31 026</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr">
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
         <is>
           <t>j3PKcB4E</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Alemannia Aachen</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>63WsD2ei</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Holstein Kiel</t>
         </is>
       </c>
-      <c r="M14" t="n">
-        <v>59</v>
-      </c>
-      <c r="N14" t="n">
+      <c r="K23" t="n">
+        <v>59</v>
+      </c>
+      <c r="L23" t="n">
         <v>593</v>
       </c>
-      <c r="O14" t="n">
+      <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>CpiTEcOi</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>17.08.2024 13:00</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
         <is>
           <t>Schüco Arena
  (Bielefeld)</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>27 332</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr">
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
         <is>
           <t>pp38UXK8</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Arminia Bielefeld</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>dfNCCCzS</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Hannover</t>
         </is>
       </c>
-      <c r="M15" t="n">
-        <v>59</v>
-      </c>
-      <c r="N15" t="n">
+      <c r="K24" t="n">
+        <v>59</v>
+      </c>
+      <c r="L24" t="n">
         <v>593</v>
       </c>
-      <c r="O15" t="n">
+      <c r="M24" t="n">
         <v>1</v>
       </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>8CpxDyg4</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>17.08.2024 13:00</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
         <is>
           <t>Stadion Lohmühle
  (Lubeck)</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>17 849</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr">
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
         <is>
           <t>I1Vk6k3R</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Phonix Lubeck</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>nP1i5US1</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Dortmund</t>
         </is>
       </c>
-      <c r="M16" t="n">
-        <v>59</v>
-      </c>
-      <c r="N16" t="n">
+      <c r="K25" t="n">
+        <v>59</v>
+      </c>
+      <c r="L25" t="n">
         <v>593</v>
       </c>
-      <c r="O16" t="n">
+      <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>6q2yrHgU</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>18.08.2024 08:00</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
         <is>
           <t>Ludwigspark Stadion
  (Saarbrücken)</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>16 003</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr">
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
         <is>
           <t>fLbhmJ5l</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Saarbrucken</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>6FDqshzF</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Nurnberg</t>
         </is>
       </c>
-      <c r="M17" t="n">
-        <v>59</v>
-      </c>
-      <c r="N17" t="n">
+      <c r="K26" t="n">
+        <v>59</v>
+      </c>
+      <c r="L26" t="n">
         <v>593</v>
       </c>
-      <c r="O17" t="n">
+      <c r="M26" t="n">
         <v>1</v>
       </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>AiJ3kset</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>18.08.2024 08:00</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Friedrich Ludwig Jahn Sportpark
+ (Berlin)</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>19 708</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>UNr2EUfd</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Viktoria Berlin</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="K27" t="n">
+        <v>59</v>
+      </c>
+      <c r="L27" t="n">
+        <v>593</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>18.08.2024 08:00</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>UNr2EUfd</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Viktoria Berlin</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Augsburg</t>
-        </is>
-      </c>
-      <c r="M18" t="n">
-        <v>59</v>
-      </c>
-      <c r="N18" t="n">
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>YV3TqwPH</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>18.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Stadion am Panzenberg
+ (Bremen)</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>5 000</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>tW75B1ei</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Bremer</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>G2Op923t</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>Paderborn</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>59</v>
+      </c>
+      <c r="L28" t="n">
         <v>593</v>
       </c>
-      <c r="O18" t="n">
+      <c r="M28" t="n">
         <v>1</v>
       </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>YV3TqwPH</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>l0ueP5rR</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>18.08.2024 10:30</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>tW75B1ei</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Bremer</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>G2Op923t</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>Paderborn</t>
-        </is>
-      </c>
-      <c r="M19" t="n">
-        <v>59</v>
-      </c>
-      <c r="N19" t="n">
-        <v>593</v>
-      </c>
-      <c r="O19" t="n">
-        <v>1</v>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>l0ueP5rR</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>18.08.2024 10:30</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
         <is>
           <t>Ostseestadion
  (Rostock)</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>29 000</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr">
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
         <is>
           <t>KIHmtCkL</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Hansa Rostock</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>2y0u8Wrq</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Hertha Berlin</t>
         </is>
       </c>
-      <c r="M20" t="n">
-        <v>59</v>
-      </c>
-      <c r="N20" t="n">
+      <c r="K29" t="n">
+        <v>59</v>
+      </c>
+      <c r="L29" t="n">
         <v>593</v>
       </c>
-      <c r="O20" t="n">
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>t2AoZLAa</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>18.08.2024 10:30</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
         <is>
           <t>Friedrich-Ebert-Stadium
  (Hildesheim)</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>10 000</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr">
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
         <is>
           <t>E3xs5mIe</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Hildesheim</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>6in2Eknb</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Elversberg</t>
         </is>
       </c>
-      <c r="M21" t="n">
-        <v>59</v>
-      </c>
-      <c r="N21" t="n">
+      <c r="K30" t="n">
+        <v>59</v>
+      </c>
+      <c r="L30" t="n">
         <v>593</v>
       </c>
-      <c r="O21" t="n">
+      <c r="M30" t="n">
         <v>1</v>
       </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>jFMCm08e</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>18.08.2024 10:30</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
         <is>
           <t>Jahnstadion Regensburg
  (Regensburg)</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>15 210</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr">
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
         <is>
           <t>UiCmEP56</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Regensburg</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>8Y2m6ADe</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Bochum</t>
         </is>
       </c>
-      <c r="M22" t="n">
-        <v>59</v>
-      </c>
-      <c r="N22" t="n">
+      <c r="K31" t="n">
+        <v>59</v>
+      </c>
+      <c r="L31" t="n">
         <v>593</v>
       </c>
-      <c r="O22" t="n">
+      <c r="M31" t="n">
         <v>1</v>
       </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>tvOIPExA</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>18.08.2024 10:30</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
         <is>
           <t>Hardtwaldstadion
  (Sandhausen)</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>15 414</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr">
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
         <is>
           <t>UZxEj1R4</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Sandhausen</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>WG9pOTse</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>FC Koln</t>
         </is>
       </c>
-      <c r="M23" t="n">
-        <v>59</v>
-      </c>
-      <c r="N23" t="n">
+      <c r="K32" t="n">
+        <v>59</v>
+      </c>
+      <c r="L32" t="n">
         <v>593</v>
       </c>
-      <c r="O23" t="n">
+      <c r="M32" t="n">
         <v>1</v>
       </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
         <is>
           <t>KSwfVwAO</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>18.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Millerntor-Stadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>29 546</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>WrbkcjCd</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>Teutonia Ottensen</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>S0hPB9rA</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Darmstadt</t>
+        </is>
+      </c>
+      <c r="K33" t="n">
+        <v>59</v>
+      </c>
+      <c r="L33" t="n">
+        <v>593</v>
+      </c>
+      <c r="M33" t="n">
+        <v>1</v>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>18.08.2024 10:30</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>WrbkcjCd</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Teutonia Ottensen</t>
-        </is>
-      </c>
-      <c r="K24" t="inlineStr">
-        <is>
-          <t>S0hPB9rA</t>
-        </is>
-      </c>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>Darmstadt</t>
-        </is>
-      </c>
-      <c r="M24" t="n">
-        <v>59</v>
-      </c>
-      <c r="N24" t="n">
-        <v>593</v>
-      </c>
-      <c r="O24" t="n">
-        <v>1</v>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
         <is>
           <t>pzHxyrtm</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>18.08.2024 13:00</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
         <is>
           <t>Stadion am Lotter Kreuz
  (Lotte)</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>10 059</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr">
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
         <is>
           <t>hjNlCFPB</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>Lotte</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>EB3q7jbk</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Karlsruher SC</t>
         </is>
       </c>
-      <c r="M25" t="n">
-        <v>59</v>
-      </c>
-      <c r="N25" t="n">
+      <c r="K34" t="n">
+        <v>59</v>
+      </c>
+      <c r="L34" t="n">
         <v>593</v>
       </c>
-      <c r="O25" t="n">
+      <c r="M34" t="n">
         <v>1</v>
       </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
         <is>
           <t>dCPKovw8</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>18.08.2024 13:00</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
         <is>
           <t>Hansch-Arena
  (Meppen)</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>13 696</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr">
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
         <is>
           <t>rXqBh2xP</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Meppen</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>v9k3aY5F</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Hamburger SV</t>
         </is>
       </c>
-      <c r="M26" t="n">
-        <v>59</v>
-      </c>
-      <c r="N26" t="n">
+      <c r="K35" t="n">
+        <v>59</v>
+      </c>
+      <c r="L35" t="n">
         <v>593</v>
       </c>
-      <c r="O26" t="n">
+      <c r="M35" t="n">
         <v>1</v>
       </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
         <is>
           <t>vXAKoaf5</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>18.08.2024 13:00</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
         <is>
           <t>Rudolf-Harbig-Stadion
  (Dresden)</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>32 249</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr">
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
         <is>
           <t>zL1YsOi1</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>SG Dynamo Dresden</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>ne1oL3y7</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Dusseldorf</t>
         </is>
       </c>
-      <c r="M27" t="n">
-        <v>59</v>
-      </c>
-      <c r="N27" t="n">
+      <c r="K36" t="n">
+        <v>59</v>
+      </c>
+      <c r="L36" t="n">
         <v>593</v>
       </c>
-      <c r="O27" t="n">
+      <c r="M36" t="n">
         <v>1</v>
       </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
         <is>
           <t>06NAdG8N</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>19.08.2024 13:00</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
         <is>
           <t>Stadion der Freundschaft
  (Cottbus)</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>22 450</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr">
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
         <is>
           <t>6g44VD52</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Cottbus</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>Ig1f1fy3</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Werder Bremen</t>
         </is>
       </c>
-      <c r="M28" t="n">
-        <v>59</v>
-      </c>
-      <c r="N28" t="n">
+      <c r="K37" t="n">
+        <v>59</v>
+      </c>
+      <c r="L37" t="n">
         <v>593</v>
       </c>
-      <c r="O28" t="n">
+      <c r="M37" t="n">
         <v>1</v>
       </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
         <is>
           <t>Sff03OL7</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>19.08.2024 13:00</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
         <is>
           <t>Bieberer Berg Stadion
  (Offenbach am Main)</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>20 500</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr">
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
         <is>
           <t>YJURlaIO</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Offenbach</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>YFuz2RLm</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Magdeburg</t>
         </is>
       </c>
-      <c r="M29" t="n">
-        <v>59</v>
-      </c>
-      <c r="N29" t="n">
+      <c r="K38" t="n">
+        <v>59</v>
+      </c>
+      <c r="L38" t="n">
         <v>593</v>
       </c>
-      <c r="O29" t="n">
+      <c r="M38" t="n">
         <v>1</v>
       </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
         <is>
           <t>EkP2bxvB</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>19.08.2024 13:00</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
         <is>
           <t>Stadion Oberwerth
  (Koblenz)</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>9 500</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr">
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
         <is>
           <t>p8wBsqZt</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>TuS Koblenz</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>nwkTahLL</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>Wolfsburg</t>
         </is>
       </c>
-      <c r="M30" t="n">
-        <v>59</v>
-      </c>
-      <c r="N30" t="n">
+      <c r="K39" t="n">
+        <v>59</v>
+      </c>
+      <c r="L39" t="n">
         <v>593</v>
       </c>
-      <c r="O30" t="n">
+      <c r="M39" t="n">
         <v>1</v>
       </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
         <is>
           <t>pAXo2Kvn</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>19.08.2024 15:45</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
         <is>
           <t>Eintracht-Stadion
  (Braunschweig)</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>23 325</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr">
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
         <is>
           <t>QqLCC3il</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>Braunschweig</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>8vndvXTk</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Eintracht Frankfurt</t>
         </is>
       </c>
-      <c r="M31" t="n">
-        <v>59</v>
-      </c>
-      <c r="N31" t="n">
+      <c r="K40" t="n">
+        <v>59</v>
+      </c>
+      <c r="L40" t="n">
         <v>593</v>
       </c>
-      <c r="O31" t="n">
+      <c r="M40" t="n">
         <v>1</v>
       </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>W67CmLPh</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>27.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Preussenstadion
+ (Munster)</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>12 794</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>zedZaSL7</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>Preussen Munster</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>59</v>
+      </c>
+      <c r="L41" t="n">
+        <v>593</v>
+      </c>
+      <c r="M41" t="n">
+        <v>1</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>DFB Pokal</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
         <is>
           <t>fcxqFy2l</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Super Cup</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
+      <c r="B42" t="inlineStr">
         <is>
           <t>17.08.2024 15:30</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
         <is>
           <t>BayArena
  (Leverkusen)</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="E42" t="inlineStr">
         <is>
           <t>30 210</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr">
+      <c r="F42" t="inlineStr"/>
+      <c r="G42" t="inlineStr">
         <is>
           <t>4jcj2zMd</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>Bayer Leverkusen</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="I42" t="inlineStr">
         <is>
           <t>nJQmYp1B</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="J42" t="inlineStr">
         <is>
           <t>Stuttgart</t>
         </is>
       </c>
-      <c r="M32" t="n">
-        <v>59</v>
-      </c>
-      <c r="N32" t="n">
+      <c r="K42" t="n">
+        <v>59</v>
+      </c>
+      <c r="L42" t="n">
         <v>594</v>
       </c>
-      <c r="O32" t="n">
+      <c r="M42" t="n">
         <v>1</v>
       </c>
-      <c r="P32" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>2024</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Super Cup</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P33"/>
+  <dimension ref="A1:P41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -577,2137 +577,2689 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>YZZcMwBs</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>16.08.2024 13:00</t>
+          <t>24.08.2024 10:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
+          <t>WWK Arena
+ (Augsburg)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>30 660</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>59</v>
+      </c>
+      <c r="L3" t="n">
+        <v>591</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>GbeXvnR8</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>24.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Europa-Park Stadion
+ (Freiburg)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>34 700</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>59</v>
+      </c>
+      <c r="L4" t="n">
+        <v>591</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>O48oHrZ1</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>24.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PreZero Arena
+ (Sinsheim)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>30 150</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>59</v>
+      </c>
+      <c r="L5" t="n">
+        <v>591</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2FREIeA6</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>24.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Mewa Arena
+ (Mainz)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>34 000</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>59</v>
+      </c>
+      <c r="L6" t="n">
+        <v>591</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>dfO6OQtS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>24.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Red Bull Arena
+ (Leipzig)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>47 069</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>59</v>
+      </c>
+      <c r="L7" t="n">
+        <v>591</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>SxFxJ44k</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>24.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Signal Iduna Park
+ (Dortmund)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>81 365</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>59</v>
+      </c>
+      <c r="L8" t="n">
+        <v>591</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>t0w6KHuf</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>25.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Volkswagen Arena
+ (Wolfsburg)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>28 917</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>59</v>
+      </c>
+      <c r="L9" t="n">
+        <v>591</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AuVMGZvJ</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>25.08.2024 12:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Millerntor-Stadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>29 546</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>59</v>
+      </c>
+      <c r="L10" t="n">
+        <v>591</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>pWQQJq6l</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>16.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
           <t>Leuna Chemie Stadion
  (Halle)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>15 057</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
         <is>
           <t>boX3cIQa</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Hallescher</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I11" t="inlineStr">
         <is>
           <t>ILyJuN3g</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J11" t="inlineStr">
         <is>
           <t>St. Pauli</t>
         </is>
       </c>
-      <c r="K3" t="n">
-        <v>59</v>
-      </c>
-      <c r="L3" t="n">
+      <c r="K11" t="n">
+        <v>59</v>
+      </c>
+      <c r="L11" t="n">
         <v>593</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M11" t="n">
         <v>1</v>
       </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
         <is>
           <t>hIsO3XFj</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>16.08.2024 13:00</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr">
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
         <is>
           <t>BRITA-Arena
  (Wiesbaden)</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E12" t="inlineStr">
         <is>
           <t>12 566</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
         <is>
           <t>ObxFt3lm</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>Wehen</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I12" t="inlineStr">
         <is>
           <t>EuakNmc1</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="J12" t="inlineStr">
         <is>
           <t>Mainz</t>
         </is>
       </c>
-      <c r="K4" t="n">
-        <v>59</v>
-      </c>
-      <c r="L4" t="n">
+      <c r="K12" t="n">
+        <v>59</v>
+      </c>
+      <c r="L12" t="n">
         <v>593</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
         <is>
           <t>EF8gXauC</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B13" t="inlineStr">
         <is>
           <t>16.08.2024 13:00</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr">
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Flyeralarm Arena
  (Wurzburger)</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>13 090</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
         <is>
           <t>nVM1YUFj</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Wurzburger Kickers</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I13" t="inlineStr">
         <is>
           <t>hQAtP9Sl</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="J13" t="inlineStr">
         <is>
           <t>Hoffenheim</t>
         </is>
       </c>
-      <c r="K5" t="n">
-        <v>59</v>
-      </c>
-      <c r="L5" t="n">
+      <c r="K13" t="n">
+        <v>59</v>
+      </c>
+      <c r="L13" t="n">
         <v>593</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M13" t="n">
         <v>1</v>
       </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
         <is>
           <t>lONsG15D</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B14" t="inlineStr">
         <is>
           <t>16.08.2024 15:45</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr">
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Donaustadion
  (Ulm)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>19 500</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>tbC3EcQn</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Ulm</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I14" t="inlineStr">
         <is>
           <t>nVp0wiqd</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="J14" t="inlineStr">
         <is>
           <t>Bayern Munich</t>
         </is>
       </c>
-      <c r="K6" t="n">
-        <v>59</v>
-      </c>
-      <c r="L6" t="n">
+      <c r="K14" t="n">
+        <v>59</v>
+      </c>
+      <c r="L14" t="n">
         <v>593</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M14" t="n">
         <v>1</v>
       </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
         <is>
           <t>0K2qBFNG</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B15" t="inlineStr">
         <is>
           <t>17.08.2024 08:00</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr">
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
         <is>
           <t>Erzgebirgsstadion
  (Aue)</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>16 485</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
         <is>
           <t>vsXIDreP</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Aue</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I15" t="inlineStr">
         <is>
           <t>88HSzjDr</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr">
+      <c r="J15" t="inlineStr">
         <is>
           <t>B. Monchengladbach</t>
         </is>
       </c>
-      <c r="K7" t="n">
-        <v>59</v>
-      </c>
-      <c r="L7" t="n">
+      <c r="K15" t="n">
+        <v>59</v>
+      </c>
+      <c r="L15" t="n">
         <v>593</v>
       </c>
-      <c r="M7" t="n">
+      <c r="M15" t="n">
         <v>1</v>
       </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Kj4sifWp</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>17.08.2024 08:00</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Bruchwegstadion
  (Mainz)</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>7 134</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
         <is>
           <t>WzEYqEyg</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Schott Mainz</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I16" t="inlineStr">
         <is>
           <t>CCQGbik8</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>Greuther Furth</t>
         </is>
       </c>
-      <c r="K8" t="n">
-        <v>59</v>
-      </c>
-      <c r="L8" t="n">
+      <c r="K16" t="n">
+        <v>59</v>
+      </c>
+      <c r="L16" t="n">
         <v>593</v>
       </c>
-      <c r="M8" t="n">
+      <c r="M16" t="n">
         <v>1</v>
       </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>bF2q76Mr</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B17" t="inlineStr">
         <is>
           <t>17.08.2024 10:30</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
         <is>
           <t>OSTALB ARENA
  (Aalen)</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>14 500</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
         <is>
           <t>Oh2C15j0</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Aalen</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I17" t="inlineStr">
         <is>
           <t>0Ija0Ej9</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr">
+      <c r="J17" t="inlineStr">
         <is>
           <t>Schalke</t>
         </is>
       </c>
-      <c r="K9" t="n">
-        <v>59</v>
-      </c>
-      <c r="L9" t="n">
+      <c r="K17" t="n">
+        <v>59</v>
+      </c>
+      <c r="L17" t="n">
         <v>593</v>
       </c>
-      <c r="M9" t="n">
+      <c r="M17" t="n">
         <v>1</v>
       </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
         <is>
           <t>vyk5gjdE</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>17.08.2024 10:30</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Volksstadion Greifswald
  (Greifswald)</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>4 990</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
         <is>
           <t>Q1yNyI5t</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Greifswald</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
+      <c r="I18" t="inlineStr">
         <is>
           <t>pzHW4oaE</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>Union Berlin</t>
         </is>
       </c>
-      <c r="K10" t="n">
-        <v>59</v>
-      </c>
-      <c r="L10" t="n">
+      <c r="K18" t="n">
+        <v>59</v>
+      </c>
+      <c r="L18" t="n">
         <v>593</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M18" t="n">
         <v>1</v>
       </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
         <is>
           <t>tbKZHNz1</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B19" t="inlineStr">
         <is>
           <t>17.08.2024 10:30</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
         <is>
           <t>Audi Sportpark
  (Ingolstadt)</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>15 800</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
         <is>
           <t>ne5QkLtB</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Ingolstadt</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr">
+      <c r="I19" t="inlineStr">
         <is>
           <t>naWckLmC</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Kaiserslautern</t>
         </is>
       </c>
-      <c r="K11" t="n">
-        <v>59</v>
-      </c>
-      <c r="L11" t="n">
+      <c r="K19" t="n">
+        <v>59</v>
+      </c>
+      <c r="L19" t="n">
         <v>593</v>
       </c>
-      <c r="M11" t="n">
+      <c r="M19" t="n">
         <v>1</v>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="1" t="inlineStr">
         <is>
           <t>MZjh9ghT</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B20" t="inlineStr">
         <is>
           <t>17.08.2024 10:30</t>
         </is>
       </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
         <is>
           <t>Stadion an der Hafenstrasse
  (Essen)</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="E20" t="inlineStr">
         <is>
           <t>20 352</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
+      <c r="F20" t="inlineStr"/>
+      <c r="G20" t="inlineStr">
         <is>
           <t>EB0xsr77</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>RW Essen</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
+      <c r="I20" t="inlineStr">
         <is>
           <t>KbS1suSm</t>
         </is>
       </c>
-      <c r="J12" t="inlineStr">
+      <c r="J20" t="inlineStr">
         <is>
           <t>RB Leipzig</t>
         </is>
       </c>
-      <c r="K12" t="n">
-        <v>59</v>
-      </c>
-      <c r="L12" t="n">
+      <c r="K20" t="n">
+        <v>59</v>
+      </c>
+      <c r="L20" t="n">
         <v>593</v>
       </c>
-      <c r="M12" t="n">
+      <c r="M20" t="n">
         <v>1</v>
       </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="1" t="inlineStr">
         <is>
           <t>f1nnRRDE</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>17.08.2024 10:30</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Stadion an der Bremer Brück
  (Osnabrück)</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>16 667</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
+      <c r="F21" t="inlineStr"/>
+      <c r="G21" t="inlineStr">
         <is>
           <t>88Xgj1Y5</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>VfL Osnabruck</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
+      <c r="I21" t="inlineStr">
         <is>
           <t>fiEQZ7C7</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J21" t="inlineStr">
         <is>
           <t>Freiburg</t>
         </is>
       </c>
-      <c r="K13" t="n">
-        <v>59</v>
-      </c>
-      <c r="L13" t="n">
+      <c r="K21" t="n">
+        <v>59</v>
+      </c>
+      <c r="L21" t="n">
         <v>593</v>
       </c>
-      <c r="M13" t="n">
+      <c r="M21" t="n">
         <v>1</v>
       </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
         <is>
           <t>8QPARz8c</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>17.08.2024 10:30</t>
         </is>
       </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
         <is>
           <t>MS Technologie Arena
  (Villingen-Schwenningen)</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>8 000</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
+      <c r="F22" t="inlineStr"/>
+      <c r="G22" t="inlineStr">
         <is>
           <t>lKLJUxeT</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>Villingen</t>
         </is>
       </c>
-      <c r="I14" t="inlineStr">
+      <c r="I22" t="inlineStr">
         <is>
           <t>KWixEVWi</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>Heidenheim</t>
         </is>
       </c>
-      <c r="K14" t="n">
-        <v>59</v>
-      </c>
-      <c r="L14" t="n">
+      <c r="K22" t="n">
+        <v>59</v>
+      </c>
+      <c r="L22" t="n">
         <v>593</v>
       </c>
-      <c r="M14" t="n">
+      <c r="M22" t="n">
         <v>1</v>
       </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="1" t="inlineStr">
         <is>
           <t>hzyf0b9b</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B23" t="inlineStr">
         <is>
           <t>17.08.2024 13:00</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
         <is>
           <t>New Tivoli
  (Aachen)</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>31 026</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
+      <c r="F23" t="inlineStr"/>
+      <c r="G23" t="inlineStr">
         <is>
           <t>j3PKcB4E</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>Alemannia Aachen</t>
         </is>
       </c>
-      <c r="I15" t="inlineStr">
+      <c r="I23" t="inlineStr">
         <is>
           <t>63WsD2ei</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr">
+      <c r="J23" t="inlineStr">
         <is>
           <t>Holstein Kiel</t>
         </is>
       </c>
-      <c r="K15" t="n">
-        <v>59</v>
-      </c>
-      <c r="L15" t="n">
+      <c r="K23" t="n">
+        <v>59</v>
+      </c>
+      <c r="L23" t="n">
         <v>593</v>
       </c>
-      <c r="M15" t="n">
+      <c r="M23" t="n">
         <v>1</v>
       </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="1" t="inlineStr">
         <is>
           <t>CpiTEcOi</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B24" t="inlineStr">
         <is>
           <t>17.08.2024 13:00</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
         <is>
           <t>Schüco Arena
  (Bielefeld)</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="E24" t="inlineStr">
         <is>
           <t>27 332</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
+      <c r="F24" t="inlineStr"/>
+      <c r="G24" t="inlineStr">
         <is>
           <t>pp38UXK8</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>Arminia Bielefeld</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
+      <c r="I24" t="inlineStr">
         <is>
           <t>dfNCCCzS</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr">
+      <c r="J24" t="inlineStr">
         <is>
           <t>Hannover</t>
         </is>
       </c>
-      <c r="K16" t="n">
-        <v>59</v>
-      </c>
-      <c r="L16" t="n">
+      <c r="K24" t="n">
+        <v>59</v>
+      </c>
+      <c r="L24" t="n">
         <v>593</v>
       </c>
-      <c r="M16" t="n">
+      <c r="M24" t="n">
         <v>1</v>
       </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="1" t="inlineStr">
         <is>
           <t>8CpxDyg4</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B25" t="inlineStr">
         <is>
           <t>17.08.2024 13:00</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
         <is>
           <t>Stadion Lohmühle
  (Lubeck)</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="E25" t="inlineStr">
         <is>
           <t>17 849</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr">
         <is>
           <t>I1Vk6k3R</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>Phonix Lubeck</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
+      <c r="I25" t="inlineStr">
         <is>
           <t>nP1i5US1</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr">
+      <c r="J25" t="inlineStr">
         <is>
           <t>Dortmund</t>
         </is>
       </c>
-      <c r="K17" t="n">
-        <v>59</v>
-      </c>
-      <c r="L17" t="n">
+      <c r="K25" t="n">
+        <v>59</v>
+      </c>
+      <c r="L25" t="n">
         <v>593</v>
       </c>
-      <c r="M17" t="n">
+      <c r="M25" t="n">
         <v>1</v>
       </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="1" t="inlineStr">
         <is>
           <t>6q2yrHgU</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B26" t="inlineStr">
         <is>
           <t>18.08.2024 08:00</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr">
         <is>
           <t>Ludwigspark Stadion
  (Saarbrücken)</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E26" t="inlineStr">
         <is>
           <t>16 003</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
+      <c r="F26" t="inlineStr"/>
+      <c r="G26" t="inlineStr">
         <is>
           <t>fLbhmJ5l</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>Saarbrucken</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="I26" t="inlineStr">
         <is>
           <t>6FDqshzF</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr">
+      <c r="J26" t="inlineStr">
         <is>
           <t>Nurnberg</t>
         </is>
       </c>
-      <c r="K18" t="n">
-        <v>59</v>
-      </c>
-      <c r="L18" t="n">
+      <c r="K26" t="n">
+        <v>59</v>
+      </c>
+      <c r="L26" t="n">
         <v>593</v>
       </c>
-      <c r="M18" t="n">
+      <c r="M26" t="n">
         <v>1</v>
       </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
         <is>
           <t>AiJ3kset</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>18.08.2024 08:00</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
         <is>
           <t>Friedrich Ludwig Jahn Sportpark
  (Berlin)</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>19 708</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
         <is>
           <t>UNr2EUfd</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>Viktoria Berlin</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="I27" t="inlineStr">
         <is>
           <t>fTVNku3I</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>Augsburg</t>
         </is>
       </c>
-      <c r="K19" t="n">
-        <v>59</v>
-      </c>
-      <c r="L19" t="n">
+      <c r="K27" t="n">
+        <v>59</v>
+      </c>
+      <c r="L27" t="n">
         <v>593</v>
       </c>
-      <c r="M19" t="n">
+      <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
         <is>
           <t>YV3TqwPH</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>18.08.2024 10:30</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
         <is>
           <t>Stadion am Panzenberg
  (Bremen)</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>5 000</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
+      <c r="F28" t="inlineStr"/>
+      <c r="G28" t="inlineStr">
         <is>
           <t>tW75B1ei</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>Bremer</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr">
+      <c r="I28" t="inlineStr">
         <is>
           <t>G2Op923t</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr">
+      <c r="J28" t="inlineStr">
         <is>
           <t>Paderborn</t>
         </is>
       </c>
-      <c r="K20" t="n">
-        <v>59</v>
-      </c>
-      <c r="L20" t="n">
+      <c r="K28" t="n">
+        <v>59</v>
+      </c>
+      <c r="L28" t="n">
         <v>593</v>
       </c>
-      <c r="M20" t="n">
+      <c r="M28" t="n">
         <v>1</v>
       </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
         <is>
           <t>l0ueP5rR</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>18.08.2024 10:30</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr">
         <is>
           <t>Ostseestadion
  (Rostock)</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E29" t="inlineStr">
         <is>
           <t>29 000</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr">
         <is>
           <t>KIHmtCkL</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>Hansa Rostock</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
+      <c r="I29" t="inlineStr">
         <is>
           <t>2y0u8Wrq</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J29" t="inlineStr">
         <is>
           <t>Hertha Berlin</t>
         </is>
       </c>
-      <c r="K21" t="n">
-        <v>59</v>
-      </c>
-      <c r="L21" t="n">
+      <c r="K29" t="n">
+        <v>59</v>
+      </c>
+      <c r="L29" t="n">
         <v>593</v>
       </c>
-      <c r="M21" t="n">
+      <c r="M29" t="n">
         <v>1</v>
       </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
         <is>
           <t>t2AoZLAa</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>18.08.2024 10:30</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
         <is>
           <t>Friedrich-Ebert-Stadium
  (Hildesheim)</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>10 000</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
+      <c r="F30" t="inlineStr"/>
+      <c r="G30" t="inlineStr">
         <is>
           <t>E3xs5mIe</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>Hildesheim</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
+      <c r="I30" t="inlineStr">
         <is>
           <t>6in2Eknb</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr">
+      <c r="J30" t="inlineStr">
         <is>
           <t>Elversberg</t>
         </is>
       </c>
-      <c r="K22" t="n">
-        <v>59</v>
-      </c>
-      <c r="L22" t="n">
+      <c r="K30" t="n">
+        <v>59</v>
+      </c>
+      <c r="L30" t="n">
         <v>593</v>
       </c>
-      <c r="M22" t="n">
+      <c r="M30" t="n">
         <v>1</v>
       </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
         <is>
           <t>jFMCm08e</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B31" t="inlineStr">
         <is>
           <t>18.08.2024 10:30</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
         <is>
           <t>Jahnstadion Regensburg
  (Regensburg)</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="E31" t="inlineStr">
         <is>
           <t>15 210</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
         <is>
           <t>UiCmEP56</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>Regensburg</t>
         </is>
       </c>
-      <c r="I23" t="inlineStr">
+      <c r="I31" t="inlineStr">
         <is>
           <t>8Y2m6ADe</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr">
+      <c r="J31" t="inlineStr">
         <is>
           <t>Bochum</t>
         </is>
       </c>
-      <c r="K23" t="n">
-        <v>59</v>
-      </c>
-      <c r="L23" t="n">
+      <c r="K31" t="n">
+        <v>59</v>
+      </c>
+      <c r="L31" t="n">
         <v>593</v>
       </c>
-      <c r="M23" t="n">
+      <c r="M31" t="n">
         <v>1</v>
       </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>tvOIPExA</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
+      <c r="B32" t="inlineStr">
         <is>
           <t>18.08.2024 10:30</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
         <is>
           <t>Hardtwaldstadion
  (Sandhausen)</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="E32" t="inlineStr">
         <is>
           <t>15 414</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
+      <c r="F32" t="inlineStr"/>
+      <c r="G32" t="inlineStr">
         <is>
           <t>UZxEj1R4</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>Sandhausen</t>
         </is>
       </c>
-      <c r="I24" t="inlineStr">
+      <c r="I32" t="inlineStr">
         <is>
           <t>WG9pOTse</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr">
+      <c r="J32" t="inlineStr">
         <is>
           <t>FC Koln</t>
         </is>
       </c>
-      <c r="K24" t="n">
-        <v>59</v>
-      </c>
-      <c r="L24" t="n">
+      <c r="K32" t="n">
+        <v>59</v>
+      </c>
+      <c r="L32" t="n">
         <v>593</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M32" t="n">
         <v>1</v>
       </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
         <is>
           <t>KSwfVwAO</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>18.08.2024 10:30</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr">
         <is>
           <t>Millerntor-Stadion
  (Hamburg)</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="E33" t="inlineStr">
         <is>
           <t>29 546</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
+      <c r="F33" t="inlineStr"/>
+      <c r="G33" t="inlineStr">
         <is>
           <t>WrbkcjCd</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>Teutonia Ottensen</t>
         </is>
       </c>
-      <c r="I25" t="inlineStr">
+      <c r="I33" t="inlineStr">
         <is>
           <t>S0hPB9rA</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr">
+      <c r="J33" t="inlineStr">
         <is>
           <t>Darmstadt</t>
         </is>
       </c>
-      <c r="K25" t="n">
-        <v>59</v>
-      </c>
-      <c r="L25" t="n">
+      <c r="K33" t="n">
+        <v>59</v>
+      </c>
+      <c r="L33" t="n">
         <v>593</v>
       </c>
-      <c r="M25" t="n">
+      <c r="M33" t="n">
         <v>1</v>
       </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
         <is>
           <t>pzHxyrtm</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B34" t="inlineStr">
         <is>
           <t>18.08.2024 13:00</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
         <is>
           <t>Stadion am Lotter Kreuz
  (Lotte)</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E34" t="inlineStr">
         <is>
           <t>10 059</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr">
         <is>
           <t>hjNlCFPB</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>Lotte</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
+      <c r="I34" t="inlineStr">
         <is>
           <t>EB3q7jbk</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr">
+      <c r="J34" t="inlineStr">
         <is>
           <t>Karlsruher SC</t>
         </is>
       </c>
-      <c r="K26" t="n">
-        <v>59</v>
-      </c>
-      <c r="L26" t="n">
+      <c r="K34" t="n">
+        <v>59</v>
+      </c>
+      <c r="L34" t="n">
         <v>593</v>
       </c>
-      <c r="M26" t="n">
+      <c r="M34" t="n">
         <v>1</v>
       </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
         <is>
           <t>dCPKovw8</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B35" t="inlineStr">
         <is>
           <t>18.08.2024 13:00</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
         <is>
           <t>Hansch-Arena
  (Meppen)</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E35" t="inlineStr">
         <is>
           <t>13 696</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
+      <c r="F35" t="inlineStr"/>
+      <c r="G35" t="inlineStr">
         <is>
           <t>rXqBh2xP</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>Meppen</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="I35" t="inlineStr">
         <is>
           <t>v9k3aY5F</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr">
+      <c r="J35" t="inlineStr">
         <is>
           <t>Hamburger SV</t>
         </is>
       </c>
-      <c r="K27" t="n">
-        <v>59</v>
-      </c>
-      <c r="L27" t="n">
+      <c r="K35" t="n">
+        <v>59</v>
+      </c>
+      <c r="L35" t="n">
         <v>593</v>
       </c>
-      <c r="M27" t="n">
+      <c r="M35" t="n">
         <v>1</v>
       </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
         <is>
           <t>vXAKoaf5</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B36" t="inlineStr">
         <is>
           <t>18.08.2024 13:00</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr">
         <is>
           <t>Rudolf-Harbig-Stadion
  (Dresden)</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E36" t="inlineStr">
         <is>
           <t>32 249</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr">
         <is>
           <t>zL1YsOi1</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>SG Dynamo Dresden</t>
         </is>
       </c>
-      <c r="I28" t="inlineStr">
+      <c r="I36" t="inlineStr">
         <is>
           <t>ne1oL3y7</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr">
+      <c r="J36" t="inlineStr">
         <is>
           <t>Dusseldorf</t>
         </is>
       </c>
-      <c r="K28" t="n">
-        <v>59</v>
-      </c>
-      <c r="L28" t="n">
+      <c r="K36" t="n">
+        <v>59</v>
+      </c>
+      <c r="L36" t="n">
         <v>593</v>
       </c>
-      <c r="M28" t="n">
+      <c r="M36" t="n">
         <v>1</v>
       </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
         <is>
           <t>06NAdG8N</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
+      <c r="B37" t="inlineStr">
         <is>
           <t>19.08.2024 13:00</t>
         </is>
       </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
         <is>
           <t>Stadion der Freundschaft
  (Cottbus)</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="E37" t="inlineStr">
         <is>
           <t>22 450</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
+      <c r="F37" t="inlineStr"/>
+      <c r="G37" t="inlineStr">
         <is>
           <t>6g44VD52</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>Cottbus</t>
         </is>
       </c>
-      <c r="I29" t="inlineStr">
+      <c r="I37" t="inlineStr">
         <is>
           <t>Ig1f1fy3</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr">
+      <c r="J37" t="inlineStr">
         <is>
           <t>Werder Bremen</t>
         </is>
       </c>
-      <c r="K29" t="n">
-        <v>59</v>
-      </c>
-      <c r="L29" t="n">
+      <c r="K37" t="n">
+        <v>59</v>
+      </c>
+      <c r="L37" t="n">
         <v>593</v>
       </c>
-      <c r="M29" t="n">
+      <c r="M37" t="n">
         <v>1</v>
       </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
         <is>
           <t>Sff03OL7</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
+      <c r="B38" t="inlineStr">
         <is>
           <t>19.08.2024 13:00</t>
         </is>
       </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr">
         <is>
           <t>Bieberer Berg Stadion
  (Offenbach am Main)</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>20 500</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr">
         <is>
           <t>YJURlaIO</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>Offenbach</t>
         </is>
       </c>
-      <c r="I30" t="inlineStr">
+      <c r="I38" t="inlineStr">
         <is>
           <t>YFuz2RLm</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
+      <c r="J38" t="inlineStr">
         <is>
           <t>Magdeburg</t>
         </is>
       </c>
-      <c r="K30" t="n">
-        <v>59</v>
-      </c>
-      <c r="L30" t="n">
+      <c r="K38" t="n">
+        <v>59</v>
+      </c>
+      <c r="L38" t="n">
         <v>593</v>
       </c>
-      <c r="M30" t="n">
+      <c r="M38" t="n">
         <v>1</v>
       </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P38" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
         <is>
           <t>EkP2bxvB</t>
         </is>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B39" t="inlineStr">
         <is>
           <t>19.08.2024 13:00</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr">
         <is>
           <t>Stadion Oberwerth
  (Koblenz)</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="E39" t="inlineStr">
         <is>
           <t>9 500</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
+      <c r="F39" t="inlineStr"/>
+      <c r="G39" t="inlineStr">
         <is>
           <t>p8wBsqZt</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>TuS Koblenz</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
+      <c r="I39" t="inlineStr">
         <is>
           <t>nwkTahLL</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr">
+      <c r="J39" t="inlineStr">
         <is>
           <t>Wolfsburg</t>
         </is>
       </c>
-      <c r="K31" t="n">
-        <v>59</v>
-      </c>
-      <c r="L31" t="n">
+      <c r="K39" t="n">
+        <v>59</v>
+      </c>
+      <c r="L39" t="n">
         <v>593</v>
       </c>
-      <c r="M31" t="n">
+      <c r="M39" t="n">
         <v>1</v>
       </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P39" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
         <is>
           <t>pAXo2Kvn</t>
         </is>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B40" t="inlineStr">
         <is>
           <t>19.08.2024 15:45</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr">
         <is>
           <t>Eintracht-Stadion
  (Braunschweig)</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="E40" t="inlineStr">
         <is>
           <t>23 325</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr">
         <is>
           <t>QqLCC3il</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>Braunschweig</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr">
+      <c r="I40" t="inlineStr">
         <is>
           <t>8vndvXTk</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr">
+      <c r="J40" t="inlineStr">
         <is>
           <t>Eintracht Frankfurt</t>
         </is>
       </c>
-      <c r="K32" t="n">
-        <v>59</v>
-      </c>
-      <c r="L32" t="n">
+      <c r="K40" t="n">
+        <v>59</v>
+      </c>
+      <c r="L40" t="n">
         <v>593</v>
       </c>
-      <c r="M32" t="n">
+      <c r="M40" t="n">
         <v>1</v>
       </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
         <is>
           <t>fcxqFy2l</t>
         </is>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>17.08.2024 15:30</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
         <is>
           <t>BayArena
  (Leverkusen)</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="E41" t="inlineStr">
         <is>
           <t>30 210</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
+      <c r="F41" t="inlineStr"/>
+      <c r="G41" t="inlineStr">
         <is>
           <t>4jcj2zMd</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>Bayer Leverkusen</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
+      <c r="I41" t="inlineStr">
         <is>
           <t>nJQmYp1B</t>
         </is>
       </c>
-      <c r="J33" t="inlineStr">
+      <c r="J41" t="inlineStr">
         <is>
           <t>Stuttgart</t>
         </is>
       </c>
-      <c r="K33" t="n">
-        <v>59</v>
-      </c>
-      <c r="L33" t="n">
+      <c r="K41" t="n">
+        <v>59</v>
+      </c>
+      <c r="L41" t="n">
         <v>594</v>
       </c>
-      <c r="M33" t="n">
+      <c r="M41" t="n">
         <v>1</v>
       </c>
-      <c r="N33" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
+      <c r="O41" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
         <is>
           <t>Super Cup</t>
         </is>

--- a/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:P25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,35 +1129,35 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16.08.2024 13:00</t>
+          <t>30.08.2024 15:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Leuna Chemie Stadion
- (Halle)</t>
+          <t>Stadion An der Alten Försterei
+ (Berlin)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>15 057</t>
+          <t>22 012</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>boX3cIQa</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Hallescher</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1174,10 +1174,10 @@
         <v>59</v>
       </c>
       <c r="L11" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1191,62 +1191,62 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16.08.2024 13:00</t>
+          <t>31.08.2024 10:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BRITA-Arena
- (Wiesbaden)</t>
+          <t>Vonovia Ruhrstadion
+ (Bochum)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12 566</t>
+          <t>26 000</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ObxFt3lm</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Wehen</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>B. Monchengladbach</t>
         </is>
       </c>
       <c r="K12" t="n">
         <v>59</v>
       </c>
       <c r="L12" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16.08.2024 13:00</t>
+          <t>31.08.2024 10:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Flyeralarm Arena
- (Wurzburger)</t>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13 090</t>
+          <t>58 000</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>nVM1YUFj</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Wurzburger Kickers</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1312,10 +1312,10 @@
         <v>59</v>
       </c>
       <c r="L13" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1329,62 +1329,62 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16.08.2024 15:45</t>
+          <t>31.08.2024 10:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Donaustadion
- (Ulm)</t>
+          <t>Holstein-Stadion
+ (Kiel)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19 500</t>
+          <t>15 034</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tbC3EcQn</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="K14" t="n">
         <v>59</v>
       </c>
       <c r="L14" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1398,62 +1398,62 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17.08.2024 08:00</t>
+          <t>31.08.2024 10:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Erzgebirgsstadion
- (Aue)</t>
+          <t>MHPArena
+ (Stuttgart)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16 485</t>
+          <t>60 449</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>vsXIDreP</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Aue</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>B. Monchengladbach</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="K15" t="n">
         <v>59</v>
       </c>
       <c r="L15" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1467,62 +1467,62 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17.08.2024 08:00</t>
+          <t>31.08.2024 10:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bruchwegstadion
- (Mainz)</t>
+          <t>Weserstadion
+ (Bremen)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7 134</t>
+          <t>42 100</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>WzEYqEyg</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schott Mainz</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CCQGbik8</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Greuther Furth</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="K16" t="n">
         <v>59</v>
       </c>
       <c r="L16" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1536,62 +1536,62 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17.08.2024 10:30</t>
+          <t>31.08.2024 13:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>OSTALB ARENA
- (Aalen)</t>
+          <t>BayArena
+ (Leverkusen)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14 500</t>
+          <t>30 210</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Oh2C15j0</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Aalen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Schalke</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="K17" t="n">
         <v>59</v>
       </c>
       <c r="L17" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1605,62 +1605,62 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17.08.2024 10:30</t>
+          <t>01.09.2024 10:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Volksstadion Greifswald
- (Greifswald)</t>
+          <t>Voith-Arena
+ (Heidenheim)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4 990</t>
+          <t>15 000</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Q1yNyI5t</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Greifswald</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="K18" t="n">
         <v>59</v>
       </c>
       <c r="L18" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1674,62 +1674,62 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17.08.2024 10:30</t>
+          <t>01.09.2024 12:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Audi Sportpark
- (Ingolstadt)</t>
+          <t>Allianz Arena
+ (Munich)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>15 800</t>
+          <t>75 024</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ne5QkLtB</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>naWckLmC</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="K19" t="n">
         <v>59</v>
       </c>
       <c r="L19" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1743,52 +1743,57 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>06NAdG8N</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17.08.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
+          <t>19.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Osmers H.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Stadion an der Hafenstrasse
- (Essen)</t>
+          <t>Stadion der Freundschaft
+ (Cottbus)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20 352</t>
+          <t>22 450</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>EB0xsr77</t>
+          <t>6g44VD52</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>RW Essen</t>
+          <t>Cottbus</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1819,45 +1824,50 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>Sff03OL7</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17.08.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
+          <t>19.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Alt P.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Stadion an der Bremer Brück
- (Osnabrück)</t>
+          <t>Bieberer Berg Stadion
+ (Offenbach am Main)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>16 667</t>
+          <t>20 500</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>88Xgj1Y5</t>
+          <t>YJURlaIO</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>VfL Osnabruck</t>
+          <t>Offenbach</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>YFuz2RLm</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Magdeburg</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1888,45 +1898,50 @@
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
+          <t>EkP2bxvB</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>17.08.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
+          <t>19.08.2024 13:00</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Storks S.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>MS Technologie Arena
- (Villingen-Schwenningen)</t>
+          <t>Stadion Oberwerth
+ (Koblenz)</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>8 000</t>
+          <t>9 500</t>
         </is>
       </c>
       <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>lKLJUxeT</t>
+          <t>p8wBsqZt</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>Villingen</t>
+          <t>TuS Koblenz</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -1957,45 +1972,50 @@
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>pAXo2Kvn</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>17.08.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
+          <t>19.08.2024 15:45</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Exner F.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>New Tivoli
- (Aachen)</t>
+          <t>Eintracht-Stadion
+ (Braunschweig)</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>31 026</t>
+          <t>23 325</t>
         </is>
       </c>
       <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
-          <t>j3PKcB4E</t>
+          <t>QqLCC3il</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Alemannia Aachen</t>
+          <t>Braunschweig</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="K23" t="n">
@@ -2026,45 +2046,45 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>W67CmLPh</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>17.08.2024 13:00</t>
+          <t>27.08.2024 15:45</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Schüco Arena
- (Bielefeld)</t>
+          <t>Preussenstadion
+ (Munster)</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>27 332</t>
+          <t>12 794</t>
         </is>
       </c>
       <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
-          <t>pp38UXK8</t>
+          <t>zedZaSL7</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Arminia Bielefeld</t>
+          <t>Preussen Munster</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>dfNCCCzS</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Hannover</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -2095,45 +2115,45 @@
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>6u6i5pie</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>17.08.2024 13:00</t>
+          <t>28.08.2024 13:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Stadion Lohmühle
- (Lubeck)</t>
+          <t>Ernst Abbe Sportfeld
+ (Jena)</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>17 849</t>
+          <t>10 445</t>
         </is>
       </c>
       <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
-          <t>I1Vk6k3R</t>
+          <t>APNl8MIn</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Phonix Lubeck</t>
+          <t>Jena</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -2158,1110 +2178,6 @@
       <c r="P25" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>6q2yrHgU</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>18.08.2024 08:00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Ludwigspark Stadion
- (Saarbrücken)</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>16 003</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>fLbhmJ5l</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Saarbrucken</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>6FDqshzF</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Nurnberg</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>59</v>
-      </c>
-      <c r="L26" t="n">
-        <v>593</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>AiJ3kset</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>18.08.2024 08:00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Friedrich Ludwig Jahn Sportpark
- (Berlin)</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>19 708</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>UNr2EUfd</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Viktoria Berlin</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Augsburg</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
-        <v>59</v>
-      </c>
-      <c r="L27" t="n">
-        <v>593</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>YV3TqwPH</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>18.08.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Stadion am Panzenberg
- (Bremen)</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>5 000</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>tW75B1ei</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Bremer</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>G2Op923t</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Paderborn</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
-        <v>59</v>
-      </c>
-      <c r="L28" t="n">
-        <v>593</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>l0ueP5rR</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>18.08.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Ostseestadion
- (Rostock)</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>29 000</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>KIHmtCkL</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Hansa Rostock</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2y0u8Wrq</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Hertha Berlin</t>
-        </is>
-      </c>
-      <c r="K29" t="n">
-        <v>59</v>
-      </c>
-      <c r="L29" t="n">
-        <v>593</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1</v>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>t2AoZLAa</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>18.08.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Friedrich-Ebert-Stadium
- (Hildesheim)</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>10 000</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>E3xs5mIe</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Hildesheim</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>6in2Eknb</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Elversberg</t>
-        </is>
-      </c>
-      <c r="K30" t="n">
-        <v>59</v>
-      </c>
-      <c r="L30" t="n">
-        <v>593</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>jFMCm08e</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>18.08.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Jahnstadion Regensburg
- (Regensburg)</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>15 210</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>UiCmEP56</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Regensburg</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>8Y2m6ADe</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Bochum</t>
-        </is>
-      </c>
-      <c r="K31" t="n">
-        <v>59</v>
-      </c>
-      <c r="L31" t="n">
-        <v>593</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1</v>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>tvOIPExA</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>18.08.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Hardtwaldstadion
- (Sandhausen)</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>15 414</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>UZxEj1R4</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Sandhausen</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>FC Koln</t>
-        </is>
-      </c>
-      <c r="K32" t="n">
-        <v>59</v>
-      </c>
-      <c r="L32" t="n">
-        <v>593</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1</v>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>KSwfVwAO</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>18.08.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Millerntor-Stadion
- (Hamburg)</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>29 546</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>WrbkcjCd</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Teutonia Ottensen</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>S0hPB9rA</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Darmstadt</t>
-        </is>
-      </c>
-      <c r="K33" t="n">
-        <v>59</v>
-      </c>
-      <c r="L33" t="n">
-        <v>593</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1</v>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>pzHxyrtm</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>18.08.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Stadion am Lotter Kreuz
- (Lotte)</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>10 059</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>hjNlCFPB</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Lotte</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>EB3q7jbk</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Karlsruher SC</t>
-        </is>
-      </c>
-      <c r="K34" t="n">
-        <v>59</v>
-      </c>
-      <c r="L34" t="n">
-        <v>593</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1</v>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>dCPKovw8</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>18.08.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Hansch-Arena
- (Meppen)</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>13 696</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>rXqBh2xP</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Meppen</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Hamburger SV</t>
-        </is>
-      </c>
-      <c r="K35" t="n">
-        <v>59</v>
-      </c>
-      <c r="L35" t="n">
-        <v>593</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1</v>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>vXAKoaf5</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>18.08.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Rudolf-Harbig-Stadion
- (Dresden)</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>32 249</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>zL1YsOi1</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>SG Dynamo Dresden</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>ne1oL3y7</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Dusseldorf</t>
-        </is>
-      </c>
-      <c r="K36" t="n">
-        <v>59</v>
-      </c>
-      <c r="L36" t="n">
-        <v>593</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1</v>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>06NAdG8N</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>19.08.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Stadion der Freundschaft
- (Cottbus)</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>22 450</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>6g44VD52</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Cottbus</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Werder Bremen</t>
-        </is>
-      </c>
-      <c r="K37" t="n">
-        <v>59</v>
-      </c>
-      <c r="L37" t="n">
-        <v>593</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1</v>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Sff03OL7</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>19.08.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Bieberer Berg Stadion
- (Offenbach am Main)</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>20 500</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>YJURlaIO</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Offenbach</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>YFuz2RLm</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Magdeburg</t>
-        </is>
-      </c>
-      <c r="K38" t="n">
-        <v>59</v>
-      </c>
-      <c r="L38" t="n">
-        <v>593</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>EkP2bxvB</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>19.08.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Stadion Oberwerth
- (Koblenz)</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>9 500</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>p8wBsqZt</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>TuS Koblenz</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Wolfsburg</t>
-        </is>
-      </c>
-      <c r="K39" t="n">
-        <v>59</v>
-      </c>
-      <c r="L39" t="n">
-        <v>593</v>
-      </c>
-      <c r="M39" t="n">
-        <v>1</v>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>pAXo2Kvn</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>19.08.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Eintracht-Stadion
- (Braunschweig)</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>23 325</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>QqLCC3il</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Braunschweig</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Eintracht Frankfurt</t>
-        </is>
-      </c>
-      <c r="K40" t="n">
-        <v>59</v>
-      </c>
-      <c r="L40" t="n">
-        <v>593</v>
-      </c>
-      <c r="M40" t="n">
-        <v>1</v>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>fcxqFy2l</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>17.08.2024 15:30</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>BayArena
- (Leverkusen)</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>30 210</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Bayer Leverkusen</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Stuttgart</t>
-        </is>
-      </c>
-      <c r="K41" t="n">
-        <v>59</v>
-      </c>
-      <c r="L41" t="n">
-        <v>594</v>
-      </c>
-      <c r="M41" t="n">
-        <v>1</v>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Super Cup</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P41"/>
+  <dimension ref="A1:P21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1129,35 +1129,35 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>16.08.2024 13:00</t>
+          <t>30.08.2024 15:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Leuna Chemie Stadion
- (Halle)</t>
+          <t>Stadion An der Alten Försterei
+ (Berlin)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>15 057</t>
+          <t>22 012</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>boX3cIQa</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Hallescher</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1174,10 +1174,10 @@
         <v>59</v>
       </c>
       <c r="L11" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
@@ -1191,62 +1191,62 @@
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>16.08.2024 13:00</t>
+          <t>31.08.2024 10:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>BRITA-Arena
- (Wiesbaden)</t>
+          <t>Vonovia Ruhrstadion
+ (Bochum)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>12 566</t>
+          <t>26 000</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>ObxFt3lm</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Wehen</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>B. Monchengladbach</t>
         </is>
       </c>
       <c r="K12" t="n">
         <v>59</v>
       </c>
       <c r="L12" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>16.08.2024 13:00</t>
+          <t>31.08.2024 10:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Flyeralarm Arena
- (Wurzburger)</t>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>13 090</t>
+          <t>58 000</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>nVM1YUFj</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Wurzburger Kickers</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1312,10 +1312,10 @@
         <v>59</v>
       </c>
       <c r="L13" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
@@ -1329,62 +1329,62 @@
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>16.08.2024 15:45</t>
+          <t>31.08.2024 10:30</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Donaustadion
- (Ulm)</t>
+          <t>Holstein-Stadion
+ (Kiel)</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>19 500</t>
+          <t>15 034</t>
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
-          <t>tbC3EcQn</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Ulm</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="K14" t="n">
         <v>59</v>
       </c>
       <c r="L14" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N14" t="inlineStr">
         <is>
@@ -1398,62 +1398,62 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>17.08.2024 08:00</t>
+          <t>31.08.2024 10:30</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Erzgebirgsstadion
- (Aue)</t>
+          <t>MHPArena
+ (Stuttgart)</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>16 485</t>
+          <t>60 449</t>
         </is>
       </c>
       <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
-          <t>vsXIDreP</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Aue</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>B. Monchengladbach</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="K15" t="n">
         <v>59</v>
       </c>
       <c r="L15" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N15" t="inlineStr">
         <is>
@@ -1467,62 +1467,62 @@
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>17.08.2024 08:00</t>
+          <t>31.08.2024 10:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr"/>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Bruchwegstadion
- (Mainz)</t>
+          <t>Weserstadion
+ (Bremen)</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7 134</t>
+          <t>42 100</t>
         </is>
       </c>
       <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
-          <t>WzEYqEyg</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schott Mainz</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>CCQGbik8</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>Greuther Furth</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="K16" t="n">
         <v>59</v>
       </c>
       <c r="L16" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M16" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N16" t="inlineStr">
         <is>
@@ -1536,62 +1536,62 @@
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>17.08.2024 10:30</t>
+          <t>31.08.2024 13:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr"/>
       <c r="D17" t="inlineStr">
         <is>
-          <t>OSTALB ARENA
- (Aalen)</t>
+          <t>BayArena
+ (Leverkusen)</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>14 500</t>
+          <t>30 210</t>
         </is>
       </c>
       <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Oh2C15j0</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Aalen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>0Ija0Ej9</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>Schalke</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="K17" t="n">
         <v>59</v>
       </c>
       <c r="L17" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M17" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N17" t="inlineStr">
         <is>
@@ -1605,62 +1605,62 @@
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>17.08.2024 10:30</t>
+          <t>01.09.2024 10:30</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Volksstadion Greifswald
- (Greifswald)</t>
+          <t>Voith-Arena
+ (Heidenheim)</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>4 990</t>
+          <t>15 000</t>
         </is>
       </c>
       <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Q1yNyI5t</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Greifswald</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="K18" t="n">
         <v>59</v>
       </c>
       <c r="L18" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M18" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N18" t="inlineStr">
         <is>
@@ -1674,62 +1674,62 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>17.08.2024 10:30</t>
+          <t>01.09.2024 12:30</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Audi Sportpark
- (Ingolstadt)</t>
+          <t>Allianz Arena
+ (Munich)</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>15 800</t>
+          <t>75 024</t>
         </is>
       </c>
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>ne5QkLtB</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Ingolstadt</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>naWckLmC</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>Kaiserslautern</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="K19" t="n">
         <v>59</v>
       </c>
       <c r="L19" t="n">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="M19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N19" t="inlineStr">
         <is>
@@ -1743,52 +1743,52 @@
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>DFB Pokal</t>
+          <t>Bundesliga</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>W67CmLPh</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>17.08.2024 10:30</t>
+          <t>27.08.2024 15:45</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Stadion an der Hafenstrasse
- (Essen)</t>
+          <t>Preussenstadion
+ (Munster)</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>20 352</t>
+          <t>12 794</t>
         </is>
       </c>
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>EB0xsr77</t>
+          <t>zedZaSL7</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>RW Essen</t>
+          <t>Preussen Munster</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -1819,45 +1819,45 @@
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>6u6i5pie</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>17.08.2024 10:30</t>
+          <t>28.08.2024 13:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Stadion an der Bremer Brück
- (Osnabrück)</t>
+          <t>Ernst Abbe Sportfeld
+ (Jena)</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>16 667</t>
+          <t>10 445</t>
         </is>
       </c>
       <c r="F21" t="inlineStr"/>
       <c r="G21" t="inlineStr">
         <is>
-          <t>88Xgj1Y5</t>
+          <t>APNl8MIn</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>VfL Osnabruck</t>
+          <t>Jena</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -1882,1386 +1882,6 @@
       <c r="P21" t="inlineStr">
         <is>
           <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>8QPARz8c</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>17.08.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>MS Technologie Arena
- (Villingen-Schwenningen)</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>8 000</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>lKLJUxeT</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>Villingen</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>Heidenheim</t>
-        </is>
-      </c>
-      <c r="K22" t="n">
-        <v>59</v>
-      </c>
-      <c r="L22" t="n">
-        <v>593</v>
-      </c>
-      <c r="M22" t="n">
-        <v>1</v>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>hzyf0b9b</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>17.08.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>New Tivoli
- (Aachen)</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>31 026</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>j3PKcB4E</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>Alemannia Aachen</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>63WsD2ei</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>Holstein Kiel</t>
-        </is>
-      </c>
-      <c r="K23" t="n">
-        <v>59</v>
-      </c>
-      <c r="L23" t="n">
-        <v>593</v>
-      </c>
-      <c r="M23" t="n">
-        <v>1</v>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>CpiTEcOi</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>17.08.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Schüco Arena
- (Bielefeld)</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>27 332</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>pp38UXK8</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>Arminia Bielefeld</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>dfNCCCzS</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>Hannover</t>
-        </is>
-      </c>
-      <c r="K24" t="n">
-        <v>59</v>
-      </c>
-      <c r="L24" t="n">
-        <v>593</v>
-      </c>
-      <c r="M24" t="n">
-        <v>1</v>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>8CpxDyg4</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>17.08.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Stadion Lohmühle
- (Lubeck)</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>17 849</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>I1Vk6k3R</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Phonix Lubeck</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>Dortmund</t>
-        </is>
-      </c>
-      <c r="K25" t="n">
-        <v>59</v>
-      </c>
-      <c r="L25" t="n">
-        <v>593</v>
-      </c>
-      <c r="M25" t="n">
-        <v>1</v>
-      </c>
-      <c r="N25" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O25" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>6q2yrHgU</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>18.08.2024 08:00</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Ludwigspark Stadion
- (Saarbrücken)</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>16 003</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>fLbhmJ5l</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Saarbrucken</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>6FDqshzF</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>Nurnberg</t>
-        </is>
-      </c>
-      <c r="K26" t="n">
-        <v>59</v>
-      </c>
-      <c r="L26" t="n">
-        <v>593</v>
-      </c>
-      <c r="M26" t="n">
-        <v>1</v>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>AiJ3kset</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>18.08.2024 08:00</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Friedrich Ludwig Jahn Sportpark
- (Berlin)</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>19 708</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>UNr2EUfd</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Viktoria Berlin</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>Augsburg</t>
-        </is>
-      </c>
-      <c r="K27" t="n">
-        <v>59</v>
-      </c>
-      <c r="L27" t="n">
-        <v>593</v>
-      </c>
-      <c r="M27" t="n">
-        <v>1</v>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>YV3TqwPH</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>18.08.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Stadion am Panzenberg
- (Bremen)</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>5 000</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>tW75B1ei</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Bremer</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>G2Op923t</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>Paderborn</t>
-        </is>
-      </c>
-      <c r="K28" t="n">
-        <v>59</v>
-      </c>
-      <c r="L28" t="n">
-        <v>593</v>
-      </c>
-      <c r="M28" t="n">
-        <v>1</v>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>l0ueP5rR</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>18.08.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Ostseestadion
- (Rostock)</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>29 000</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>KIHmtCkL</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Hansa Rostock</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2y0u8Wrq</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>Hertha Berlin</t>
-        </is>
-      </c>
-      <c r="K29" t="n">
-        <v>59</v>
-      </c>
-      <c r="L29" t="n">
-        <v>593</v>
-      </c>
-      <c r="M29" t="n">
-        <v>1</v>
-      </c>
-      <c r="N29" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O29" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>t2AoZLAa</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>18.08.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Friedrich-Ebert-Stadium
- (Hildesheim)</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>10 000</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>E3xs5mIe</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Hildesheim</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>6in2Eknb</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>Elversberg</t>
-        </is>
-      </c>
-      <c r="K30" t="n">
-        <v>59</v>
-      </c>
-      <c r="L30" t="n">
-        <v>593</v>
-      </c>
-      <c r="M30" t="n">
-        <v>1</v>
-      </c>
-      <c r="N30" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O30" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>jFMCm08e</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>18.08.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Jahnstadion Regensburg
- (Regensburg)</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>15 210</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>UiCmEP56</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Regensburg</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>8Y2m6ADe</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>Bochum</t>
-        </is>
-      </c>
-      <c r="K31" t="n">
-        <v>59</v>
-      </c>
-      <c r="L31" t="n">
-        <v>593</v>
-      </c>
-      <c r="M31" t="n">
-        <v>1</v>
-      </c>
-      <c r="N31" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>tvOIPExA</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>18.08.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Hardtwaldstadion
- (Sandhausen)</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>15 414</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>UZxEj1R4</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Sandhausen</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>WG9pOTse</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>FC Koln</t>
-        </is>
-      </c>
-      <c r="K32" t="n">
-        <v>59</v>
-      </c>
-      <c r="L32" t="n">
-        <v>593</v>
-      </c>
-      <c r="M32" t="n">
-        <v>1</v>
-      </c>
-      <c r="N32" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>KSwfVwAO</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>18.08.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Millerntor-Stadion
- (Hamburg)</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>29 546</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>WrbkcjCd</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Teutonia Ottensen</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>S0hPB9rA</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>Darmstadt</t>
-        </is>
-      </c>
-      <c r="K33" t="n">
-        <v>59</v>
-      </c>
-      <c r="L33" t="n">
-        <v>593</v>
-      </c>
-      <c r="M33" t="n">
-        <v>1</v>
-      </c>
-      <c r="N33" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>pzHxyrtm</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>18.08.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Stadion am Lotter Kreuz
- (Lotte)</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>10 059</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>hjNlCFPB</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Lotte</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>EB3q7jbk</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>Karlsruher SC</t>
-        </is>
-      </c>
-      <c r="K34" t="n">
-        <v>59</v>
-      </c>
-      <c r="L34" t="n">
-        <v>593</v>
-      </c>
-      <c r="M34" t="n">
-        <v>1</v>
-      </c>
-      <c r="N34" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>dCPKovw8</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>18.08.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Hansch-Arena
- (Meppen)</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>13 696</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>rXqBh2xP</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Meppen</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>v9k3aY5F</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>Hamburger SV</t>
-        </is>
-      </c>
-      <c r="K35" t="n">
-        <v>59</v>
-      </c>
-      <c r="L35" t="n">
-        <v>593</v>
-      </c>
-      <c r="M35" t="n">
-        <v>1</v>
-      </c>
-      <c r="N35" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>vXAKoaf5</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>18.08.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Rudolf-Harbig-Stadion
- (Dresden)</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>32 249</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>zL1YsOi1</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>SG Dynamo Dresden</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>ne1oL3y7</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>Dusseldorf</t>
-        </is>
-      </c>
-      <c r="K36" t="n">
-        <v>59</v>
-      </c>
-      <c r="L36" t="n">
-        <v>593</v>
-      </c>
-      <c r="M36" t="n">
-        <v>1</v>
-      </c>
-      <c r="N36" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O36" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P36" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>06NAdG8N</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>19.08.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Stadion der Freundschaft
- (Cottbus)</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>22 450</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>6g44VD52</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Cottbus</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>Werder Bremen</t>
-        </is>
-      </c>
-      <c r="K37" t="n">
-        <v>59</v>
-      </c>
-      <c r="L37" t="n">
-        <v>593</v>
-      </c>
-      <c r="M37" t="n">
-        <v>1</v>
-      </c>
-      <c r="N37" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O37" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P37" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Sff03OL7</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>19.08.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Bieberer Berg Stadion
- (Offenbach am Main)</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>20 500</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>YJURlaIO</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Offenbach</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>YFuz2RLm</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>Magdeburg</t>
-        </is>
-      </c>
-      <c r="K38" t="n">
-        <v>59</v>
-      </c>
-      <c r="L38" t="n">
-        <v>593</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1</v>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>EkP2bxvB</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>19.08.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Stadion Oberwerth
- (Koblenz)</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>9 500</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>p8wBsqZt</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>TuS Koblenz</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>Wolfsburg</t>
-        </is>
-      </c>
-      <c r="K39" t="n">
-        <v>59</v>
-      </c>
-      <c r="L39" t="n">
-        <v>593</v>
-      </c>
-      <c r="M39" t="n">
-        <v>1</v>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>pAXo2Kvn</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>19.08.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Eintracht-Stadion
- (Braunschweig)</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>23 325</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>QqLCC3il</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Braunschweig</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>Eintracht Frankfurt</t>
-        </is>
-      </c>
-      <c r="K40" t="n">
-        <v>59</v>
-      </c>
-      <c r="L40" t="n">
-        <v>593</v>
-      </c>
-      <c r="M40" t="n">
-        <v>1</v>
-      </c>
-      <c r="N40" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P40" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>fcxqFy2l</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>17.08.2024 15:30</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>BayArena
- (Leverkusen)</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>30 210</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Bayer Leverkusen</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>Stuttgart</t>
-        </is>
-      </c>
-      <c r="K41" t="n">
-        <v>59</v>
-      </c>
-      <c r="L41" t="n">
-        <v>594</v>
-      </c>
-      <c r="M41" t="n">
-        <v>1</v>
-      </c>
-      <c r="N41" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="O41" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P41" t="inlineStr">
-        <is>
-          <t>Super Cup</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1747,144 +1747,6 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>W67CmLPh</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>27.08.2024 15:45</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Preussenstadion
- (Munster)</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>12 794</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>zedZaSL7</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>Preussen Munster</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>Stuttgart</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>59</v>
-      </c>
-      <c r="L20" t="n">
-        <v>593</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1</v>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>6u6i5pie</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>28.08.2024 13:00</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Ernst Abbe Sportfeld
- (Jena)</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>10 445</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>APNl8MIn</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Jena</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>Bayer Leverkusen</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>59</v>
-      </c>
-      <c r="L21" t="n">
-        <v>593</v>
-      </c>
-      <c r="M21" t="n">
-        <v>1</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>DFB Pokal</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,50 +508,50 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>YZZcMwBs</t>
+          <t>t0w6KHuf</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>24.08.2024 10:30</t>
+          <t>25.08.2024 10:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Stegemann S.
+          <t>Siebert D.
  (Ger)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>WWK Arena
- (Augsburg)</t>
+          <t>Volkswagen Arena
+ (Wolfsburg)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30 660</t>
+          <t>28 917</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -582,50 +582,50 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GbeXvnR8</t>
+          <t>AuVMGZvJ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>24.08.2024 10:30</t>
+          <t>25.08.2024 12:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Welz T.
+          <t>Jablonski S.
  (Ger)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Europa-Park Stadion
- (Freiburg)</t>
+          <t>Millerntor-Stadion
+ (Hamburg)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>34 700</t>
+          <t>29 546</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -656,50 +656,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>24.08.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Stieler T.
- (Ger)</t>
-        </is>
-      </c>
+          <t>30.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>PreZero Arena
- (Sinsheim)</t>
+          <t>Stadion An der Alten Försterei
+ (Berlin)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>30 150</t>
+          <t>22 012</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -730,50 +725,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.08.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Osmers H.
- (Ger)</t>
-        </is>
-      </c>
+          <t>31.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Mewa Arena
- (Mainz)</t>
+          <t>Vonovia Ruhrstadion
+ (Bochum)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>34 000</t>
+          <t>26 000</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>B. Monchengladbach</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -804,50 +794,45 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24.08.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Brand B.
- (Ger)</t>
-        </is>
-      </c>
+          <t>31.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Red Bull Arena
- (Leipzig)</t>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>47 069</t>
+          <t>58 000</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -878,50 +863,45 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SxFxJ44k</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>24.08.2024 13:30</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Zwayer F.
- (Ger)</t>
-        </is>
-      </c>
+          <t>31.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Signal Iduna Park
- (Dortmund)</t>
+          <t>Holstein-Stadion
+ (Kiel)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>81 365</t>
+          <t>15 034</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -944,6 +924,351 @@
         </is>
       </c>
       <c r="P7" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>61DvZGfm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>31.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>MHPArena
+ (Stuttgart)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>60 449</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>59</v>
+      </c>
+      <c r="L8" t="n">
+        <v>591</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>0OYDmG9t</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>31.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Weserstadion
+ (Bremen)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>42 100</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>59</v>
+      </c>
+      <c r="L9" t="n">
+        <v>591</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AVR8vwXP</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>31.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>BayArena
+ (Leverkusen)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>30 210</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>59</v>
+      </c>
+      <c r="L10" t="n">
+        <v>591</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>W8b4TCOO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>01.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Voith-Arena
+ (Heidenheim)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>59</v>
+      </c>
+      <c r="L11" t="n">
+        <v>591</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2T6mXfPa</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>01.09.2024 12:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Allianz Arena
+ (Munich)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>75 024</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>59</v>
+      </c>
+      <c r="L12" t="n">
+        <v>591</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P12"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,50 +508,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>t0w6KHuf</t>
+          <t>djSMofvg</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>25.08.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Siebert D.
- (Ger)</t>
-        </is>
-      </c>
+          <t>30.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Volkswagen Arena
- (Wolfsburg)</t>
+          <t>Stadion An der Alten Försterei
+ (Berlin)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>28 917</t>
+          <t>22 012</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -582,50 +577,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>AuVMGZvJ</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>25.08.2024 12:30</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Jablonski S.
- (Ger)</t>
-        </is>
-      </c>
+          <t>31.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Millerntor-Stadion
- (Hamburg)</t>
+          <t>Vonovia Ruhrstadion
+ (Bochum)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>29 546</t>
+          <t>26 000</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>B. Monchengladbach</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -656,45 +646,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>djSMofvg</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>30.08.2024 15:30</t>
+          <t>31.08.2024 10:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Stadion An der Alten Försterei
- (Berlin)</t>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>22 012</t>
+          <t>58 000</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -725,7 +715,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>U3QUqY85</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -736,34 +726,34 @@
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Vonovia Ruhrstadion
- (Bochum)</t>
+          <t>Holstein-Stadion
+ (Kiel)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>26 000</t>
+          <t>15 034</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>B. Monchengladbach</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -794,7 +784,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>AgAeVYgC</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -805,34 +795,34 @@
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Deutsche Bank Park
- (Frankfurt)</t>
+          <t>MHPArena
+ (Stuttgart)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>58 000</t>
+          <t>60 449</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -863,7 +853,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>QVJwrCwI</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -874,34 +864,34 @@
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Holstein-Stadion
- (Kiel)</t>
+          <t>Weserstadion
+ (Bremen)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15 034</t>
+          <t>42 100</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -932,45 +922,45 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>61DvZGfm</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>31.08.2024 10:30</t>
+          <t>31.08.2024 13:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>MHPArena
- (Stuttgart)</t>
+          <t>BayArena
+ (Leverkusen)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>60 449</t>
+          <t>30 210</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -1001,45 +991,45 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>0OYDmG9t</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>31.08.2024 10:30</t>
+          <t>01.09.2024 10:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Weserstadion
- (Bremen)</t>
+          <t>Voith-Arena
+ (Heidenheim)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>42 100</t>
+          <t>15 000</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1070,45 +1060,45 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>AVR8vwXP</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>31.08.2024 13:30</t>
+          <t>01.09.2024 12:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>BayArena
- (Leverkusen)</t>
+          <t>Allianz Arena
+ (Munich)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30 210</t>
+          <t>75 024</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1131,144 +1121,6 @@
         </is>
       </c>
       <c r="P10" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>W8b4TCOO</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>01.09.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Voith-Arena
- (Heidenheim)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>15 000</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Heidenheim</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Augsburg</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>59</v>
-      </c>
-      <c r="L11" t="n">
-        <v>591</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2T6mXfPa</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>01.09.2024 12:30</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Allianz Arena
- (Munich)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>75 024</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>nVp0wiqd</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Bayern Munich</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Freiburg</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>59</v>
-      </c>
-      <c r="L12" t="n">
-        <v>591</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,45 +508,50 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>djSMofvg</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>30.08.2024 15:30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>31.08.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Storks S.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stadion An der Alten Försterei
- (Berlin)</t>
+          <t>Vonovia Ruhrstadion
+ (Bochum)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22 012</t>
+          <t>26 000</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>B. Monchengladbach</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -577,7 +582,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U3QUqY85</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,37 +590,42 @@
           <t>31.08.2024 10:30</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Badstubner F.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Vonovia Ruhrstadion
- (Bochum)</t>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>26 000</t>
+          <t>58 000</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>B. Monchengladbach</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -646,7 +656,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AgAeVYgC</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -654,37 +664,42 @@
           <t>31.08.2024 10:30</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Exner F.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Deutsche Bank Park
- (Frankfurt)</t>
+          <t>Holstein-Stadion
+ (Kiel)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>58 000</t>
+          <t>15 034</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -715,7 +730,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>QVJwrCwI</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -723,37 +738,42 @@
           <t>31.08.2024 10:30</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Gerach T.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Holstein-Stadion
- (Kiel)</t>
+          <t>MHPArena
+ (Stuttgart)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15 034</t>
+          <t>60 449</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -784,7 +804,7 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>61DvZGfm</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -792,37 +812,42 @@
           <t>31.08.2024 10:30</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Hartmann R.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>MHPArena
- (Stuttgart)</t>
+          <t>Weserstadion
+ (Bremen)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>60 449</t>
+          <t>42 100</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -853,45 +878,50 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>0OYDmG9t</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>31.08.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>31.08.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Jollenbeck M.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Weserstadion
- (Bremen)</t>
+          <t>BayArena
+ (Leverkusen)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>42 100</t>
+          <t>30 210</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -922,45 +952,45 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>AVR8vwXP</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>31.08.2024 13:30</t>
+          <t>01.09.2024 10:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BayArena
- (Leverkusen)</t>
+          <t>Voith-Arena
+ (Heidenheim)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30 210</t>
+          <t>15 000</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -991,45 +1021,45 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>W8b4TCOO</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>01.09.2024 10:30</t>
+          <t>01.09.2024 12:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Voith-Arena
- (Heidenheim)</t>
+          <t>Allianz Arena
+ (Munich)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>15 000</t>
+          <t>75 024</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1060,45 +1090,45 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2T6mXfPa</t>
+          <t>zsmd0ggn</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>01.09.2024 12:30</t>
+          <t>13.09.2024 15:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Allianz Arena
- (Munich)</t>
+          <t>Signal Iduna Park
+ (Dortmund)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>75 024</t>
+          <t>81 365</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1121,6 +1151,420 @@
         </is>
       </c>
       <c r="P10" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UwsvBA74</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>14.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Borussia-Park
+ (Mönchengladbach)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>54 042</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>59</v>
+      </c>
+      <c r="L11" t="n">
+        <v>591</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>vZqDdBhB</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>14.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Europa-Park Stadion
+ (Freiburg)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>34 700</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>59</v>
+      </c>
+      <c r="L12" t="n">
+        <v>591</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>r7j4bXNb</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>14.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>PreZero Arena
+ (Sinsheim)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>30 150</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>59</v>
+      </c>
+      <c r="L13" t="n">
+        <v>591</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>WSMotj8U</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>14.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Red Bull Arena
+ (Leipzig)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>47 069</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>59</v>
+      </c>
+      <c r="L14" t="n">
+        <v>591</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>tI0qkTpo</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>14.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Volkswagen Arena
+ (Wolfsburg)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>28 917</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>59</v>
+      </c>
+      <c r="L15" t="n">
+        <v>591</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>x4pn9lxH</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>14.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Holstein-Stadion
+ (Kiel)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>15 034</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>59</v>
+      </c>
+      <c r="L16" t="n">
+        <v>591</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,45 +508,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>W8b4TCOO</t>
+          <t>zsmd0ggn</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>01.09.2024 10:30</t>
+          <t>13.09.2024 15:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Voith-Arena
- (Heidenheim)</t>
+          <t>Signal Iduna Park
+ (Dortmund)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15 000</t>
+          <t>81 365</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
           <t>KWixEVWi</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>Heidenheim</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Augsburg</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -577,45 +577,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2T6mXfPa</t>
+          <t>UwsvBA74</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>01.09.2024 12:30</t>
+          <t>14.09.2024 10:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Allianz Arena
- (Munich)</t>
+          <t>Borussia-Park
+ (Mönchengladbach)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>75 024</t>
+          <t>54 042</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>B. Monchengladbach</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -638,6 +638,489 @@
         </is>
       </c>
       <c r="P3" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>vZqDdBhB</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>14.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Europa-Park Stadion
+ (Freiburg)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>34 700</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>59</v>
+      </c>
+      <c r="L4" t="n">
+        <v>591</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>r7j4bXNb</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>14.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PreZero Arena
+ (Sinsheim)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>30 150</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>59</v>
+      </c>
+      <c r="L5" t="n">
+        <v>591</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>WSMotj8U</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>14.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Red Bull Arena
+ (Leipzig)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>47 069</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>59</v>
+      </c>
+      <c r="L6" t="n">
+        <v>591</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>tI0qkTpo</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>14.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Volkswagen Arena
+ (Wolfsburg)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>28 917</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>59</v>
+      </c>
+      <c r="L7" t="n">
+        <v>591</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>x4pn9lxH</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>14.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Holstein-Stadion
+ (Kiel)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>15 034</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>59</v>
+      </c>
+      <c r="L8" t="n">
+        <v>591</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>CnrLfkNN</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>15.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>WWK Arena
+ (Augsburg)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>30 660</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>59</v>
+      </c>
+      <c r="L9" t="n">
+        <v>591</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8OhVCWxh</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>15.09.2024 12:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Mewa Arena
+ (Mainz)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>34 000</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>59</v>
+      </c>
+      <c r="L10" t="n">
+        <v>591</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1126,6 +1126,627 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>dCL13J5e</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>20.09.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>WWK Arena
+ (Augsburg)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>30 660</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>59</v>
+      </c>
+      <c r="L11" t="n">
+        <v>591</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pY1dP0SE</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>21.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Vonovia Ruhrstadion
+ (Bochum)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>26 000</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>59</v>
+      </c>
+      <c r="L12" t="n">
+        <v>591</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>QNoNA1DL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>21.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Voith-Arena
+ (Heidenheim)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>59</v>
+      </c>
+      <c r="L13" t="n">
+        <v>591</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>hvFA1cz8</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>21.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stadion An der Alten Försterei
+ (Berlin)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>22 012</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>59</v>
+      </c>
+      <c r="L14" t="n">
+        <v>591</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>AeNg5uyq</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>21.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Weserstadion
+ (Bremen)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>42 100</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>59</v>
+      </c>
+      <c r="L15" t="n">
+        <v>591</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>IcrFCNr9</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>21.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>58 000</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>59</v>
+      </c>
+      <c r="L16" t="n">
+        <v>591</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Uy2KjtMk</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>22.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>BayArena
+ (Leverkusen)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>30 210</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>59</v>
+      </c>
+      <c r="L17" t="n">
+        <v>591</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>2k0SlKj2</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>22.09.2024 12:30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>MHPArena
+ (Stuttgart)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>60 449</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>59</v>
+      </c>
+      <c r="L18" t="n">
+        <v>591</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dQ0zIIKl</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>22.09.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Millerntor-Stadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>29 546</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>59</v>
+      </c>
+      <c r="L19" t="n">
+        <v>591</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,20 +508,15 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CnrLfkNN</t>
+          <t>dCL13J5e</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15.09.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Zwayer F.
- (Ger)</t>
-        </is>
-      </c>
+          <t>20.09.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>WWK Arena
@@ -546,12 +541,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -582,72 +577,1171 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8OhVCWxh</t>
+          <t>pY1dP0SE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>15.09.2024 12:30</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Brand B.
- (Ger)</t>
-        </is>
-      </c>
+          <t>21.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
+        <is>
+          <t>Vonovia Ruhrstadion
+ (Bochum)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>26 000</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>59</v>
+      </c>
+      <c r="L3" t="n">
+        <v>591</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>QNoNA1DL</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>21.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Voith-Arena
+ (Heidenheim)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>59</v>
+      </c>
+      <c r="L4" t="n">
+        <v>591</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>hvFA1cz8</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>21.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stadion An der Alten Försterei
+ (Berlin)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>22 012</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>59</v>
+      </c>
+      <c r="L5" t="n">
+        <v>591</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>AeNg5uyq</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>21.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Weserstadion
+ (Bremen)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>42 100</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>59</v>
+      </c>
+      <c r="L6" t="n">
+        <v>591</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>IcrFCNr9</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>21.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>58 000</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>59</v>
+      </c>
+      <c r="L7" t="n">
+        <v>591</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Uy2KjtMk</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>22.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>BayArena
+ (Leverkusen)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>30 210</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>59</v>
+      </c>
+      <c r="L8" t="n">
+        <v>591</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>2k0SlKj2</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>22.09.2024 12:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>MHPArena
+ (Stuttgart)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>60 449</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>59</v>
+      </c>
+      <c r="L9" t="n">
+        <v>591</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>dQ0zIIKl</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>22.09.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Millerntor-Stadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>29 546</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>59</v>
+      </c>
+      <c r="L10" t="n">
+        <v>591</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>rsNyMnwK</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>27.09.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Signal Iduna Park
+ (Dortmund)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>81 365</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>59</v>
+      </c>
+      <c r="L11" t="n">
+        <v>591</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CIlrT3pm</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>28.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Borussia-Park
+ (Mönchengladbach)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>54 042</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>59</v>
+      </c>
+      <c r="L12" t="n">
+        <v>591</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>6uSGCr06</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>28.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Europa-Park Stadion
+ (Freiburg)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>34 700</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>59</v>
+      </c>
+      <c r="L13" t="n">
+        <v>591</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>f18BYPMP</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>28.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
         <is>
           <t>Mewa Arena
  (Mainz)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>34 000</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
         <is>
           <t>EuakNmc1</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>Mainz</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>59</v>
+      </c>
+      <c r="L14" t="n">
+        <v>591</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Q5hiEzKD</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>28.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Red Bull Arena
+ (Leipzig)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>47 069</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>59</v>
+      </c>
+      <c r="L15" t="n">
+        <v>591</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SfGPAMUI</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>28.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Volkswagen Arena
+ (Wolfsburg)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>28 917</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>59</v>
+      </c>
+      <c r="L16" t="n">
+        <v>591</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>IukqGdk1</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>28.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Allianz Arena
+ (Munich)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>75 024</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>59</v>
+      </c>
+      <c r="L17" t="n">
+        <v>591</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>pWnjRsFa</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>29.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Holstein-Stadion
+ (Kiel)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>15 034</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>59</v>
+      </c>
+      <c r="L18" t="n">
+        <v>591</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>bFO8E4Vg</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>29.09.2024 12:30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>PreZero Arena
+ (Sinsheim)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>30 150</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>Ig1f1fy3</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Werder Bremen</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="K19" t="n">
         <v>59</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L19" t="n">
         <v>591</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,45 +508,50 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>dCL13J5e</t>
+          <t>pY1dP0SE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20.09.2024 15:30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
+          <t>21.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Petersen M.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>WWK Arena
- (Augsburg)</t>
+          <t>Vonovia Ruhrstadion
+ (Bochum)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30 660</t>
+          <t>26 000</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -577,7 +582,7 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pY1dP0SE</t>
+          <t>QNoNA1DL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,37 +590,42 @@
           <t>21.09.2024 10:30</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Brand B.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Vonovia Ruhrstadion
- (Bochum)</t>
+          <t>Voith-Arena
+ (Heidenheim)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>26 000</t>
+          <t>15 000</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -646,7 +656,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>QNoNA1DL</t>
+          <t>hvFA1cz8</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -654,37 +664,42 @@
           <t>21.09.2024 10:30</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Jollenbeck M.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Voith-Arena
- (Heidenheim)</t>
+          <t>Stadion An der Alten Försterei
+ (Berlin)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15 000</t>
+          <t>22 012</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -715,7 +730,7 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hvFA1cz8</t>
+          <t>AeNg5uyq</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -723,37 +738,42 @@
           <t>21.09.2024 10:30</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Dankert B.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stadion An der Alten Försterei
- (Berlin)</t>
+          <t>Weserstadion
+ (Bremen)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22 012</t>
+          <t>42 100</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -784,45 +804,50 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>AeNg5uyq</t>
+          <t>IcrFCNr9</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>21.09.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
+          <t>21.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Welz T.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Weserstadion
- (Bremen)</t>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>42 100</t>
+          <t>58 000</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>B. Monchengladbach</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -853,45 +878,50 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>IcrFCNr9</t>
+          <t>Uy2KjtMk</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>21.09.2024 13:30</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
+          <t>22.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Stegemann S.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Deutsche Bank Park
- (Frankfurt)</t>
+          <t>BayArena
+ (Leverkusen)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58 000</t>
+          <t>30 210</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>B. Monchengladbach</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -922,45 +952,50 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Uy2KjtMk</t>
+          <t>2k0SlKj2</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>22.09.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
+          <t>22.09.2024 12:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Badstubner F.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>BayArena
- (Leverkusen)</t>
+          <t>MHPArena
+ (Stuttgart)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>30 210</t>
+          <t>60 449</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -991,45 +1026,50 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2k0SlKj2</t>
+          <t>dQ0zIIKl</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>22.09.2024 12:30</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
+          <t>22.09.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Hartmann R.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>MHPArena
- (Stuttgart)</t>
+          <t>Millerntor-Stadion
+ (Hamburg)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>60 449</t>
+          <t>29 546</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1052,696 +1092,6 @@
         </is>
       </c>
       <c r="P9" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>dQ0zIIKl</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>22.09.2024 14:30</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Millerntor-Stadion
- (Hamburg)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>29 546</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>St. Pauli</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>KbS1suSm</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>RB Leipzig</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>59</v>
-      </c>
-      <c r="L10" t="n">
-        <v>591</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>rsNyMnwK</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>27.09.2024 15:30</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Signal Iduna Park
- (Dortmund)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>81 365</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Dortmund</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>8Y2m6ADe</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Bochum</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>59</v>
-      </c>
-      <c r="L11" t="n">
-        <v>591</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>CIlrT3pm</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>28.09.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Borussia-Park
- (Mönchengladbach)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>54 042</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>88HSzjDr</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>B. Monchengladbach</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>pzHW4oaE</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Union Berlin</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>59</v>
-      </c>
-      <c r="L12" t="n">
-        <v>591</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>6uSGCr06</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>28.09.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Europa-Park Stadion
- (Freiburg)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>34 700</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Freiburg</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>St. Pauli</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>59</v>
-      </c>
-      <c r="L13" t="n">
-        <v>591</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>f18BYPMP</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>28.09.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Mewa Arena
- (Mainz)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>34 000</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Mainz</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Heidenheim</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>59</v>
-      </c>
-      <c r="L14" t="n">
-        <v>591</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Q5hiEzKD</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>28.09.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Red Bull Arena
- (Leipzig)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>47 069</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>KbS1suSm</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>RB Leipzig</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Augsburg</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>59</v>
-      </c>
-      <c r="L15" t="n">
-        <v>591</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>SfGPAMUI</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>28.09.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Volkswagen Arena
- (Wolfsburg)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>28 917</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Wolfsburg</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Stuttgart</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>59</v>
-      </c>
-      <c r="L16" t="n">
-        <v>591</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>IukqGdk1</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>28.09.2024 13:30</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Allianz Arena
- (Munich)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>75 024</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>nVp0wiqd</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Bayern Munich</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Bayer Leverkusen</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>59</v>
-      </c>
-      <c r="L17" t="n">
-        <v>591</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>pWnjRsFa</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>29.09.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Holstein-Stadion
- (Kiel)</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>15 034</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>63WsD2ei</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Holstein Kiel</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Eintracht Frankfurt</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>59</v>
-      </c>
-      <c r="L18" t="n">
-        <v>591</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>bFO8E4Vg</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>29.09.2024 12:30</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>PreZero Arena
- (Sinsheim)</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>30 150</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>hQAtP9Sl</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Hoffenheim</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Werder Bremen</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>59</v>
-      </c>
-      <c r="L19" t="n">
-        <v>591</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,146 +508,1240 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CnrLfkNN</t>
+          <t>rsNyMnwK</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>15.09.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Zwayer F.
- (Ger)</t>
-        </is>
-      </c>
+          <t>27.09.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>Signal Iduna Park
+ (Dortmund)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>81 365</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>59</v>
+      </c>
+      <c r="L2" t="n">
+        <v>591</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>CIlrT3pm</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>28.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Borussia-Park
+ (Mönchengladbach)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>54 042</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>59</v>
+      </c>
+      <c r="L3" t="n">
+        <v>591</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>6uSGCr06</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>28.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Europa-Park Stadion
+ (Freiburg)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>34 700</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>59</v>
+      </c>
+      <c r="L4" t="n">
+        <v>591</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>f18BYPMP</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>28.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Mewa Arena
+ (Mainz)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>34 000</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>59</v>
+      </c>
+      <c r="L5" t="n">
+        <v>591</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Q5hiEzKD</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>28.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Red Bull Arena
+ (Leipzig)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>47 069</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>59</v>
+      </c>
+      <c r="L6" t="n">
+        <v>591</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SfGPAMUI</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>28.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Volkswagen Arena
+ (Wolfsburg)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>28 917</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>59</v>
+      </c>
+      <c r="L7" t="n">
+        <v>591</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>IukqGdk1</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>28.09.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Allianz Arena
+ (Munich)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>75 024</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>59</v>
+      </c>
+      <c r="L8" t="n">
+        <v>591</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>pWnjRsFa</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>29.09.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Holstein-Stadion
+ (Kiel)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>15 034</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>59</v>
+      </c>
+      <c r="L9" t="n">
+        <v>591</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>bFO8E4Vg</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>29.09.2024 12:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PreZero Arena
+ (Sinsheim)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>30 150</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>59</v>
+      </c>
+      <c r="L10" t="n">
+        <v>591</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UajsPCkT</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>04.10.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
         <is>
           <t>WWK Arena
  (Augsburg)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>30 660</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
         <is>
           <t>fTVNku3I</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>Augsburg</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>59</v>
+      </c>
+      <c r="L11" t="n">
+        <v>591</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>tbtaPLqC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>05.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>BayArena
+ (Leverkusen)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>30 210</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>59</v>
+      </c>
+      <c r="L12" t="n">
+        <v>591</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ENOasf5c</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>05.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Vonovia Ruhrstadion
+ (Bochum)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>26 000</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>59</v>
+      </c>
+      <c r="L13" t="n">
+        <v>591</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>lpXDJjDj</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>05.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Stadion An der Alten Försterei
+ (Berlin)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>22 012</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>59</v>
+      </c>
+      <c r="L14" t="n">
+        <v>591</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>dnhZQYKG</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>05.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Weserstadion
+ (Bremen)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>42 100</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>59</v>
+      </c>
+      <c r="L15" t="n">
+        <v>591</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>zwD8uYZ9</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>05.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Millerntor-Stadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>29 546</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
         <is>
           <t>ILyJuN3g</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>St. Pauli</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
         <v>59</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L16" t="n">
         <v>591</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M16" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>8OhVCWxh</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>15.09.2024 12:30</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Brand B.
- (Ger)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Mewa Arena
- (Mainz)</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>34 000</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Mainz</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Werder Bremen</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>0KbQSfj4</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>06.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Voith-Arena
+ (Heidenheim)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
         <v>59</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L17" t="n">
         <v>591</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ShoJUGLi</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>06.10.2024 12:30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>58 000</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>59</v>
+      </c>
+      <c r="L18" t="n">
+        <v>591</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>nc8W6DTp</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>06.10.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>MHPArena
+ (Stuttgart)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>60 449</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
+        <v>59</v>
+      </c>
+      <c r="L19" t="n">
+        <v>591</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,7 +516,12 @@
           <t>27.09.2024 15:30</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Brych F.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Signal Iduna Park
@@ -585,7 +590,12 @@
           <t>28.09.2024 10:30</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Schlager D.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Borussia-Park
@@ -654,7 +664,12 @@
           <t>28.09.2024 10:30</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Gerach T.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Europa-Park Stadion
@@ -723,7 +738,12 @@
           <t>28.09.2024 10:30</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Exner F.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Mewa Arena
@@ -792,7 +812,12 @@
           <t>28.09.2024 10:30</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Siebert D.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>Red Bull Arena
@@ -861,7 +886,12 @@
           <t>28.09.2024 10:30</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Jablonski S.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Volkswagen Arena
@@ -930,7 +960,12 @@
           <t>28.09.2024 13:30</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Zwayer F.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr">
         <is>
           <t>Allianz Arena
@@ -1121,627 +1156,6 @@
         </is>
       </c>
       <c r="P10" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>UajsPCkT</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>04.10.2024 15:30</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>WWK Arena
- (Augsburg)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>30 660</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Augsburg</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>88HSzjDr</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>B. Monchengladbach</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>59</v>
-      </c>
-      <c r="L11" t="n">
-        <v>591</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>tbtaPLqC</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>05.10.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>BayArena
- (Leverkusen)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>30 210</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Bayer Leverkusen</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>63WsD2ei</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Holstein Kiel</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>59</v>
-      </c>
-      <c r="L12" t="n">
-        <v>591</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>ENOasf5c</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>05.10.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Vonovia Ruhrstadion
- (Bochum)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>26 000</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>8Y2m6ADe</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Bochum</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Wolfsburg</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>59</v>
-      </c>
-      <c r="L13" t="n">
-        <v>591</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>lpXDJjDj</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>05.10.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Stadion An der Alten Försterei
- (Berlin)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>22 012</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>pzHW4oaE</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Union Berlin</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Dortmund</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>59</v>
-      </c>
-      <c r="L14" t="n">
-        <v>591</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>dnhZQYKG</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>05.10.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Weserstadion
- (Bremen)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>42 100</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Werder Bremen</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Freiburg</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>59</v>
-      </c>
-      <c r="L15" t="n">
-        <v>591</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>zwD8uYZ9</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>05.10.2024 13:30</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Millerntor-Stadion
- (Hamburg)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>29 546</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>St. Pauli</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Mainz</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>59</v>
-      </c>
-      <c r="L16" t="n">
-        <v>591</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>0KbQSfj4</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>06.10.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Voith-Arena
- (Heidenheim)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>15 000</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Heidenheim</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>KbS1suSm</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>RB Leipzig</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>59</v>
-      </c>
-      <c r="L17" t="n">
-        <v>591</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>ShoJUGLi</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>06.10.2024 12:30</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Deutsche Bank Park
- (Frankfurt)</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>58 000</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Eintracht Frankfurt</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>nVp0wiqd</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Bayern Munich</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>59</v>
-      </c>
-      <c r="L18" t="n">
-        <v>591</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>nc8W6DTp</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>06.10.2024 14:30</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>MHPArena
- (Stuttgart)</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>60 449</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Stuttgart</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>hQAtP9Sl</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Hoffenheim</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>59</v>
-      </c>
-      <c r="L19" t="n">
-        <v>591</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,50 +508,50 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>rsNyMnwK</t>
+          <t>pWnjRsFa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>27.09.2024 15:30</t>
+          <t>29.09.2024 10:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Brych F.
+          <t>Stieler T.
  (Ger)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Signal Iduna Park
- (Dortmund)</t>
+          <t>Holstein-Stadion
+ (Kiel)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>81 365</t>
+          <t>15 034</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -582,50 +582,50 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>CIlrT3pm</t>
+          <t>bFO8E4Vg</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>28.09.2024 10:30</t>
+          <t>29.09.2024 12:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Schlager D.
+          <t>Reichel T.
  (Ger)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Borussia-Park
- (Mönchengladbach)</t>
+          <t>PreZero Arena
+ (Sinsheim)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>54 042</t>
+          <t>30 150</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>B. Monchengladbach</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -648,514 +648,6 @@
         </is>
       </c>
       <c r="P3" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>6uSGCr06</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>28.09.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Gerach T.
- (Ger)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Europa-Park Stadion
- (Freiburg)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>34 700</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>Freiburg</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>St. Pauli</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>59</v>
-      </c>
-      <c r="L4" t="n">
-        <v>591</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>f18BYPMP</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>28.09.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Exner F.
- (Ger)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Mewa Arena
- (Mainz)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>34 000</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>Mainz</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Heidenheim</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>59</v>
-      </c>
-      <c r="L5" t="n">
-        <v>591</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Q5hiEzKD</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>28.09.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Siebert D.
- (Ger)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Red Bull Arena
- (Leipzig)</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>47 069</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>KbS1suSm</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>RB Leipzig</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Augsburg</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
-        <v>59</v>
-      </c>
-      <c r="L6" t="n">
-        <v>591</v>
-      </c>
-      <c r="M6" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>SfGPAMUI</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>28.09.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Jablonski S.
- (Ger)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Volkswagen Arena
- (Wolfsburg)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>28 917</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Wolfsburg</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Stuttgart</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>59</v>
-      </c>
-      <c r="L7" t="n">
-        <v>591</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>IukqGdk1</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>28.09.2024 13:30</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Zwayer F.
- (Ger)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Allianz Arena
- (Munich)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>75 024</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>nVp0wiqd</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Bayern Munich</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Bayer Leverkusen</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>59</v>
-      </c>
-      <c r="L8" t="n">
-        <v>591</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>pWnjRsFa</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>29.09.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Holstein-Stadion
- (Kiel)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>15 034</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>63WsD2ei</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Holstein Kiel</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Eintracht Frankfurt</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>59</v>
-      </c>
-      <c r="L9" t="n">
-        <v>591</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>bFO8E4Vg</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>29.09.2024 12:30</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>PreZero Arena
- (Sinsheim)</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>30 150</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>hQAtP9Sl</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>Hoffenheim</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Werder Bremen</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
-        <v>59</v>
-      </c>
-      <c r="L10" t="n">
-        <v>591</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,50 +508,50 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pWnjRsFa</t>
+          <t>UajsPCkT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>29.09.2024 10:30</t>
+          <t>04.10.2024 15:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Stieler T.
+          <t>Badstubner F.
  (Ger)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Holstein-Stadion
- (Kiel)</t>
+          <t>WWK Arena
+ (Augsburg)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>15 034</t>
+          <t>30 660</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>B. Monchengladbach</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -582,72 +582,984 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bFO8E4Vg</t>
+          <t>tbtaPLqC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>29.09.2024 12:30</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+          <t>05.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>BayArena
+ (Leverkusen)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>30 210</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>59</v>
+      </c>
+      <c r="L3" t="n">
+        <v>591</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ENOasf5c</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>05.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Burda M.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Vonovia Ruhrstadion
+ (Bochum)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>26 000</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>59</v>
+      </c>
+      <c r="L4" t="n">
+        <v>591</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>lpXDJjDj</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>05.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
         <is>
           <t>Reichel T.
  (Ger)</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Stadion An der Alten Försterei
+ (Berlin)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>22 012</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>59</v>
+      </c>
+      <c r="L5" t="n">
+        <v>591</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>dnhZQYKG</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>05.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Welz T.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Weserstadion
+ (Bremen)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>42 100</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>59</v>
+      </c>
+      <c r="L6" t="n">
+        <v>591</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>zwD8uYZ9</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>05.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Dingert C.
+ (Ger)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Millerntor-Stadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>29 546</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>59</v>
+      </c>
+      <c r="L7" t="n">
+        <v>591</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>0KbQSfj4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>06.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Voith-Arena
+ (Heidenheim)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>59</v>
+      </c>
+      <c r="L8" t="n">
+        <v>591</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ShoJUGLi</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>06.10.2024 12:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>58 000</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>59</v>
+      </c>
+      <c r="L9" t="n">
+        <v>591</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>nc8W6DTp</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>06.10.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>MHPArena
+ (Stuttgart)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>60 449</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>59</v>
+      </c>
+      <c r="L10" t="n">
+        <v>591</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>z1eeWTdd</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>18.10.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Signal Iduna Park
+ (Dortmund)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>81 365</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>59</v>
+      </c>
+      <c r="L11" t="n">
+        <v>591</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>fHjVr7t2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>19.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Borussia-Park
+ (Mönchengladbach)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>54 042</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>59</v>
+      </c>
+      <c r="L12" t="n">
+        <v>591</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>r3GGwC4M</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>19.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>BayArena
+ (Leverkusen)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>30 210</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>59</v>
+      </c>
+      <c r="L13" t="n">
+        <v>591</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>M93rhBJF</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>19.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Europa-Park Stadion
+ (Freiburg)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>34 700</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>59</v>
+      </c>
+      <c r="L14" t="n">
+        <v>591</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Eq0zfXl3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>19.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
         <is>
           <t>PreZero Arena
  (Sinsheim)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>30 150</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
         <is>
           <t>hQAtP9Sl</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Hoffenheim</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Werder Bremen</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
         <v>59</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L15" t="n">
         <v>591</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M15" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>E7rNpTBk</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>19.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Mewa Arena
+ (Mainz)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>34 000</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>59</v>
+      </c>
+      <c r="L16" t="n">
+        <v>591</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P16"/>
+  <dimension ref="A1:P13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,50 +508,50 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>UajsPCkT</t>
+          <t>0KbQSfj4</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>04.10.2024 15:30</t>
+          <t>06.10.2024 10:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Badstubner F.
+          <t>Stegemann S.
  (Ger)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>WWK Arena
- (Augsburg)</t>
+          <t>Voith-Arena
+ (Heidenheim)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30 660</t>
+          <t>15 000</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>B. Monchengladbach</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -582,45 +582,50 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>tbtaPLqC</t>
+          <t>ShoJUGLi</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>05.10.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
+          <t>06.10.2024 12:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Brand B.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>BayArena
- (Leverkusen)</t>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30 210</t>
+          <t>58 000</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>63WsD2ei</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Holstein Kiel</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -651,50 +656,50 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>ENOasf5c</t>
+          <t>nc8W6DTp</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>05.10.2024 10:30</t>
+          <t>06.10.2024 14:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Burda M.
+          <t>Osmers H.
  (Ger)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Vonovia Ruhrstadion
- (Bochum)</t>
+          <t>MHPArena
+ (Stuttgart)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>26 000</t>
+          <t>60 449</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -725,50 +730,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lpXDJjDj</t>
+          <t>z1eeWTdd</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>05.10.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Reichel T.
- (Ger)</t>
-        </is>
-      </c>
+          <t>18.10.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stadion An der Alten Försterei
- (Berlin)</t>
+          <t>Signal Iduna Park
+ (Dortmund)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>22 012</t>
+          <t>81 365</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -799,50 +799,45 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dnhZQYKG</t>
+          <t>fHjVr7t2</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>05.10.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Welz T.
- (Ger)</t>
-        </is>
-      </c>
+          <t>19.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Weserstadion
- (Bremen)</t>
+          <t>Borussia-Park
+ (Mönchengladbach)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>42 100</t>
+          <t>54 042</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>B. Monchengladbach</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -873,50 +868,45 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>zwD8uYZ9</t>
+          <t>r3GGwC4M</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>05.10.2024 13:30</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Dingert C.
- (Ger)</t>
-        </is>
-      </c>
+          <t>19.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Millerntor-Stadion
- (Hamburg)</t>
+          <t>BayArena
+ (Leverkusen)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>29 546</t>
+          <t>30 210</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -947,45 +937,45 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>0KbQSfj4</t>
+          <t>M93rhBJF</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>06.10.2024 10:30</t>
+          <t>19.10.2024 10:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Voith-Arena
- (Heidenheim)</t>
+          <t>Europa-Park Stadion
+ (Freiburg)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15 000</t>
+          <t>34 700</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -1016,45 +1006,45 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>ShoJUGLi</t>
+          <t>Eq0zfXl3</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>06.10.2024 12:30</t>
+          <t>19.10.2024 10:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Deutsche Bank Park
- (Frankfurt)</t>
+          <t>PreZero Arena
+ (Sinsheim)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>58 000</t>
+          <t>30 150</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1085,45 +1075,45 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>nc8W6DTp</t>
+          <t>E7rNpTBk</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>06.10.2024 14:30</t>
+          <t>19.10.2024 10:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MHPArena
- (Stuttgart)</t>
+          <t>Mewa Arena
+ (Mainz)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>60 449</t>
+          <t>34 000</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="K10" t="n">
@@ -1154,45 +1144,45 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>z1eeWTdd</t>
+          <t>2mcmYkSq</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>18.10.2024 15:30</t>
+          <t>19.10.2024 13:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Signal Iduna Park
- (Dortmund)</t>
+          <t>Allianz Arena
+ (Munich)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>81 365</t>
+          <t>75 024</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1223,45 +1213,45 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>fHjVr7t2</t>
+          <t>nBwH6AY8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>19.10.2024 10:30</t>
+          <t>20.10.2024 10:30</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Borussia-Park
- (Mönchengladbach)</t>
+          <t>Holstein-Stadion
+ (Kiel)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>54 042</t>
+          <t>15 034</t>
         </is>
       </c>
       <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>63WsD2ei</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>B. Monchengladbach</t>
+          <t>Holstein Kiel</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>KWixEVWi</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>Heidenheim</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1292,45 +1282,45 @@
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>r3GGwC4M</t>
+          <t>rPiijklS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>19.10.2024 10:30</t>
+          <t>20.10.2024 12:30</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>BayArena
- (Leverkusen)</t>
+          <t>Volkswagen Arena
+ (Wolfsburg)</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>30 210</t>
+          <t>28 917</t>
         </is>
       </c>
       <c r="F13" t="inlineStr"/>
       <c r="G13" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>Ig1f1fy3</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Werder Bremen</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1353,213 +1343,6 @@
         </is>
       </c>
       <c r="P13" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>M93rhBJF</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>19.10.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Europa-Park Stadion
- (Freiburg)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>34 700</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Freiburg</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Augsburg</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>59</v>
-      </c>
-      <c r="L14" t="n">
-        <v>591</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Eq0zfXl3</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>19.10.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>PreZero Arena
- (Sinsheim)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>30 150</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>hQAtP9Sl</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Hoffenheim</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>8Y2m6ADe</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Bochum</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>59</v>
-      </c>
-      <c r="L15" t="n">
-        <v>591</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>E7rNpTBk</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>19.10.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Mewa Arena
- (Mainz)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>34 000</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Mainz</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>KbS1suSm</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>RB Leipzig</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>59</v>
-      </c>
-      <c r="L16" t="n">
-        <v>591</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
@@ -516,7 +516,12 @@
           <t>18.10.2024 15:30</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Jollenbeck M.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Signal Iduna Park

--- a/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P3"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,136 +508,1240 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>nBwH6AY8</t>
+          <t>4E8uaJWa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>20.10.2024 10:30</t>
+          <t>25.10.2024 15:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Mewa Arena
+ (Mainz)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>34 000</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>59</v>
+      </c>
+      <c r="L2" t="n">
+        <v>591</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>x0haJmIE</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>26.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>WWK Arena
+ (Augsburg)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>30 660</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>59</v>
+      </c>
+      <c r="L3" t="n">
+        <v>591</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ELNeaSQr</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>26.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Red Bull Arena
+ (Leipzig)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>47 069</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>59</v>
+      </c>
+      <c r="L4" t="n">
+        <v>591</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Mku6FvHt</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>26.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Millerntor-Stadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>29 546</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>59</v>
+      </c>
+      <c r="L5" t="n">
+        <v>591</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>rwXP4l3L</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>26.10.2024 10:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>MHPArena
+ (Stuttgart)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>60 449</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>59</v>
+      </c>
+      <c r="L6" t="n">
+        <v>591</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>MiACepQ7</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>26.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Weserstadion
+ (Bremen)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>42 100</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>59</v>
+      </c>
+      <c r="L7" t="n">
+        <v>591</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WQadeyWO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>27.10.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Vonovia Ruhrstadion
+ (Bochum)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>26 000</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>59</v>
+      </c>
+      <c r="L8" t="n">
+        <v>591</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ABBmcc1C</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>27.10.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Stadion An der Alten Försterei
+ (Berlin)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>22 012</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>59</v>
+      </c>
+      <c r="L9" t="n">
+        <v>591</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>zyC4c6ee</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>27.10.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Voith-Arena
+ (Heidenheim)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>15 000</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>59</v>
+      </c>
+      <c r="L10" t="n">
+        <v>591</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>IHYEDIog</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>01.11.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>BayArena
+ (Leverkusen)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>30 210</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>59</v>
+      </c>
+      <c r="L11" t="n">
+        <v>591</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>jVWMBdG5</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>02.11.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Allianz Arena
+ (Munich)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>75 024</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>59</v>
+      </c>
+      <c r="L12" t="n">
+        <v>591</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>485V7EFU</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>02.11.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>58 000</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>59</v>
+      </c>
+      <c r="L13" t="n">
+        <v>591</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8MVuSH0n</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>02.11.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PreZero Arena
+ (Sinsheim)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>30 150</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>59</v>
+      </c>
+      <c r="L14" t="n">
+        <v>591</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>2q7yHiho</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>02.11.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
           <t>Holstein-Stadion
  (Kiel)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E15" t="inlineStr">
         <is>
           <t>15 034</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
         <is>
           <t>63WsD2ei</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>Holstein Kiel</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>pzHW4oaE</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Union Berlin</t>
-        </is>
-      </c>
-      <c r="K2" t="n">
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
         <v>59</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L15" t="n">
         <v>591</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M15" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O15" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P15" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>rPiijklS</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>20.10.2024 12:30</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AoSdOZaB</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>02.11.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
         <is>
           <t>Volkswagen Arena
  (Wolfsburg)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>28 917</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
         <is>
           <t>nwkTahLL</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>Wolfsburg</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="K16" t="n">
+        <v>59</v>
+      </c>
+      <c r="L16" t="n">
+        <v>591</v>
+      </c>
+      <c r="M16" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>dr2N9zoI</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>02.11.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Signal Iduna Park
+ (Dortmund)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>81 365</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>59</v>
+      </c>
+      <c r="L17" t="n">
+        <v>591</v>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>GnZmQeVb</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>03.11.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Europa-Park Stadion
+ (Freiburg)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>34 700</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
+        <v>59</v>
+      </c>
+      <c r="L18" t="n">
+        <v>591</v>
+      </c>
+      <c r="M18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>raQ4MDUN</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>03.11.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Borussia-Park
+ (Mönchengladbach)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>54 042</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
         <is>
           <t>Ig1f1fy3</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>Werder Bremen</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="K19" t="n">
         <v>59</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L19" t="n">
         <v>591</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -516,7 +516,12 @@
           <t>25.10.2024 15:30</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Petersen M.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Mewa Arena
@@ -585,7 +590,12 @@
           <t>26.10.2024 10:30</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Welz T.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>WWK Arena
@@ -654,7 +664,12 @@
           <t>26.10.2024 10:30</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Jablonski S.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Red Bull Arena
@@ -723,7 +738,12 @@
           <t>26.10.2024 10:30</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Reichel T.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Millerntor-Stadion
@@ -792,7 +812,12 @@
           <t>26.10.2024 10:30</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Hartmann R.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>MHPArena
@@ -861,7 +886,12 @@
           <t>26.10.2024 13:30</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Badstubner F.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Weserstadion
@@ -1121,627 +1151,6 @@
         </is>
       </c>
       <c r="P10" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>IHYEDIog</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>01.11.2024 16:30</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>BayArena
- (Leverkusen)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>30 210</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Bayer Leverkusen</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Stuttgart</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>59</v>
-      </c>
-      <c r="L11" t="n">
-        <v>591</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>jVWMBdG5</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>02.11.2024 11:30</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Allianz Arena
- (Munich)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>75 024</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>nVp0wiqd</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Bayern Munich</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>pzHW4oaE</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Union Berlin</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>59</v>
-      </c>
-      <c r="L12" t="n">
-        <v>591</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>485V7EFU</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>02.11.2024 11:30</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Deutsche Bank Park
- (Frankfurt)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>58 000</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Eintracht Frankfurt</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>8Y2m6ADe</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Bochum</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>59</v>
-      </c>
-      <c r="L13" t="n">
-        <v>591</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8MVuSH0n</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>02.11.2024 11:30</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>PreZero Arena
- (Sinsheim)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>30 150</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>hQAtP9Sl</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>Hoffenheim</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>St. Pauli</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>59</v>
-      </c>
-      <c r="L14" t="n">
-        <v>591</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>2q7yHiho</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>02.11.2024 11:30</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Holstein-Stadion
- (Kiel)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>15 034</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>63WsD2ei</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Holstein Kiel</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Heidenheim</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>59</v>
-      </c>
-      <c r="L15" t="n">
-        <v>591</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>AoSdOZaB</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>02.11.2024 11:30</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Volkswagen Arena
- (Wolfsburg)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>28 917</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>Wolfsburg</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>Augsburg</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>59</v>
-      </c>
-      <c r="L16" t="n">
-        <v>591</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>dr2N9zoI</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>02.11.2024 14:30</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Signal Iduna Park
- (Dortmund)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>81 365</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Dortmund</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>KbS1suSm</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>RB Leipzig</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>59</v>
-      </c>
-      <c r="L17" t="n">
-        <v>591</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>GnZmQeVb</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>03.11.2024 11:30</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Europa-Park Stadion
- (Freiburg)</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>34 700</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Freiburg</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Mainz</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>59</v>
-      </c>
-      <c r="L18" t="n">
-        <v>591</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>raQ4MDUN</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>03.11.2024 13:30</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Borussia-Park
- (Mönchengladbach)</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>54 042</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>88HSzjDr</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>B. Monchengladbach</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Werder Bremen</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>59</v>
-      </c>
-      <c r="L19" t="n">
-        <v>591</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -508,649 +508,1240 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>4E8uaJWa</t>
+          <t>IHYEDIog</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>25.10.2024 15:30</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Petersen M.
- (Ger)</t>
-        </is>
-      </c>
+          <t>01.11.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
+        <is>
+          <t>BayArena
+ (Leverkusen)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>30 210</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>59</v>
+      </c>
+      <c r="L2" t="n">
+        <v>591</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>jVWMBdG5</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>02.11.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Allianz Arena
+ (Munich)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>75 024</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>59</v>
+      </c>
+      <c r="L3" t="n">
+        <v>591</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>485V7EFU</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>02.11.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>58 000</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>59</v>
+      </c>
+      <c r="L4" t="n">
+        <v>591</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>8MVuSH0n</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>02.11.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>PreZero Arena
+ (Sinsheim)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>30 150</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>59</v>
+      </c>
+      <c r="L5" t="n">
+        <v>591</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>2q7yHiho</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>02.11.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Holstein-Stadion
+ (Kiel)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>15 034</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>59</v>
+      </c>
+      <c r="L6" t="n">
+        <v>591</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>AoSdOZaB</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>02.11.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Volkswagen Arena
+ (Wolfsburg)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>28 917</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="K7" t="n">
+        <v>59</v>
+      </c>
+      <c r="L7" t="n">
+        <v>591</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>dr2N9zoI</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>02.11.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Signal Iduna Park
+ (Dortmund)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>81 365</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>59</v>
+      </c>
+      <c r="L8" t="n">
+        <v>591</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>GnZmQeVb</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>03.11.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Europa-Park Stadion
+ (Freiburg)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>34 700</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>EuakNmc1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Mainz</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>59</v>
+      </c>
+      <c r="L9" t="n">
+        <v>591</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>raQ4MDUN</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>03.11.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Borussia-Park
+ (Mönchengladbach)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>54 042</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>88HSzjDr</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>B. Monchengladbach</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>59</v>
+      </c>
+      <c r="L10" t="n">
+        <v>591</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>v3DAZKP9</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>08.11.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Stadion An der Alten Försterei
+ (Berlin)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>22 012</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>59</v>
+      </c>
+      <c r="L11" t="n">
+        <v>591</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>biQrHC9r</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>09.11.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Vonovia Ruhrstadion
+ (Bochum)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>26 000</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="K12" t="n">
+        <v>59</v>
+      </c>
+      <c r="L12" t="n">
+        <v>591</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>nee3ysec</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>09.11.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
         <is>
           <t>Mewa Arena
  (Mainz)</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E13" t="inlineStr">
         <is>
           <t>34 000</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr">
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
         <is>
           <t>EuakNmc1</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>Mainz</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>59</v>
+      </c>
+      <c r="L13" t="n">
+        <v>591</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>6HTjFjve</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>09.11.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Millerntor-Stadion
+ (Hamburg)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>29 546</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>ILyJuN3g</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>St. Pauli</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>59</v>
+      </c>
+      <c r="L14" t="n">
+        <v>591</v>
+      </c>
+      <c r="M14" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>YmumZjET</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>09.11.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Weserstadion
+ (Bremen)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>42 100</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>63WsD2ei</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Holstein Kiel</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>59</v>
+      </c>
+      <c r="L15" t="n">
+        <v>591</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>j5mWxZE4</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>09.11.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Red Bull Arena
+ (Leipzig)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>47 069</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
         <is>
           <t>88HSzjDr</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J16" t="inlineStr">
         <is>
           <t>B. Monchengladbach</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="K16" t="n">
         <v>59</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L16" t="n">
         <v>591</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M16" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N16" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O16" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P16" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>x0haJmIE</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>26.10.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Welz T.
- (Ger)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>UJQITUyi</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>10.11.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
         <is>
           <t>WWK Arena
  (Augsburg)</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E17" t="inlineStr">
         <is>
           <t>30 660</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr">
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
         <is>
           <t>fTVNku3I</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>Augsburg</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Dortmund</t>
-        </is>
-      </c>
-      <c r="K3" t="n">
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
         <v>59</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L17" t="n">
         <v>591</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M17" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="O17" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="P17" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>ELNeaSQr</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>26.10.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Jablonski S.
- (Ger)</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Red Bull Arena
- (Leipzig)</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>47 069</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>KbS1suSm</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>RB Leipzig</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Freiburg</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>59</v>
-      </c>
-      <c r="L4" t="n">
-        <v>591</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Mku6FvHt</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>26.10.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Reichel T.
- (Ger)</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Millerntor-Stadion
- (Hamburg)</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>29 546</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>St. Pauli</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Wolfsburg</t>
-        </is>
-      </c>
-      <c r="K5" t="n">
-        <v>59</v>
-      </c>
-      <c r="L5" t="n">
-        <v>591</v>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>rwXP4l3L</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>26.10.2024 10:30</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Hartmann R.
- (Ger)</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>UkaNveph</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>10.11.2024 13:30</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
         <is>
           <t>MHPArena
  (Stuttgart)</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>60 449</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr">
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr">
         <is>
           <t>nJQmYp1B</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>Stuttgart</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>63WsD2ei</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Holstein Kiel</t>
-        </is>
-      </c>
-      <c r="K6" t="n">
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="K18" t="n">
         <v>59</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L18" t="n">
         <v>591</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M18" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="N18" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="O18" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="P18" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>MiACepQ7</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>26.10.2024 13:30</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Badstubner F.
- (Ger)</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Weserstadion
- (Bremen)</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>42 100</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>Werder Bremen</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Bayer Leverkusen</t>
-        </is>
-      </c>
-      <c r="K7" t="n">
-        <v>59</v>
-      </c>
-      <c r="L7" t="n">
-        <v>591</v>
-      </c>
-      <c r="M7" t="n">
-        <v>0</v>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>WQadeyWO</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>27.10.2024 11:30</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Vonovia Ruhrstadion
- (Bochum)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>26 000</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>8Y2m6ADe</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Bochum</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>nVp0wiqd</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Bayern Munich</t>
-        </is>
-      </c>
-      <c r="K8" t="n">
-        <v>59</v>
-      </c>
-      <c r="L8" t="n">
-        <v>591</v>
-      </c>
-      <c r="M8" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>ABBmcc1C</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>27.10.2024 13:30</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Stadion An der Alten Försterei
- (Berlin)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>22 012</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>pzHW4oaE</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Union Berlin</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Eintracht Frankfurt</t>
-        </is>
-      </c>
-      <c r="K9" t="n">
-        <v>59</v>
-      </c>
-      <c r="L9" t="n">
-        <v>591</v>
-      </c>
-      <c r="M9" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>zyC4c6ee</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>27.10.2024 15:30</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>xMovyDqH</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>10.11.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
         <is>
           <t>Voith-Arena
  (Heidenheim)</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>15 000</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr">
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr">
         <is>
           <t>KWixEVWi</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>Heidenheim</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>hQAtP9Sl</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>Hoffenheim</t>
-        </is>
-      </c>
-      <c r="K10" t="n">
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="K19" t="n">
         <v>59</v>
       </c>
-      <c r="L10" t="n">
+      <c r="L19" t="n">
         <v>591</v>
       </c>
-      <c r="M10" t="n">
+      <c r="M19" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="O19" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="P19" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P19"/>
+  <dimension ref="A1:P10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1121,627 +1121,6 @@
         </is>
       </c>
       <c r="P10" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>v3DAZKP9</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>08.11.2024 16:30</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Stadion An der Alten Försterei
- (Berlin)</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>22 012</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>pzHW4oaE</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Union Berlin</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>fiEQZ7C7</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>Freiburg</t>
-        </is>
-      </c>
-      <c r="K11" t="n">
-        <v>59</v>
-      </c>
-      <c r="L11" t="n">
-        <v>591</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>biQrHC9r</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>09.11.2024 11:30</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Vonovia Ruhrstadion
- (Bochum)</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>26 000</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>8Y2m6ADe</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Bochum</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>4jcj2zMd</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>Bayer Leverkusen</t>
-        </is>
-      </c>
-      <c r="K12" t="n">
-        <v>59</v>
-      </c>
-      <c r="L12" t="n">
-        <v>591</v>
-      </c>
-      <c r="M12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>nee3ysec</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>09.11.2024 11:30</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Mewa Arena
- (Mainz)</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>34 000</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>EuakNmc1</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Mainz</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>nP1i5US1</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>Dortmund</t>
-        </is>
-      </c>
-      <c r="K13" t="n">
-        <v>59</v>
-      </c>
-      <c r="L13" t="n">
-        <v>591</v>
-      </c>
-      <c r="M13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O13" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>6HTjFjve</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>09.11.2024 11:30</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Millerntor-Stadion
- (Hamburg)</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>29 546</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>ILyJuN3g</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>St. Pauli</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>nVp0wiqd</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>Bayern Munich</t>
-        </is>
-      </c>
-      <c r="K14" t="n">
-        <v>59</v>
-      </c>
-      <c r="L14" t="n">
-        <v>591</v>
-      </c>
-      <c r="M14" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>YmumZjET</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>09.11.2024 11:30</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Weserstadion
- (Bremen)</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>42 100</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Ig1f1fy3</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>Werder Bremen</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>63WsD2ei</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>Holstein Kiel</t>
-        </is>
-      </c>
-      <c r="K15" t="n">
-        <v>59</v>
-      </c>
-      <c r="L15" t="n">
-        <v>591</v>
-      </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>j5mWxZE4</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>09.11.2024 14:30</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Red Bull Arena
- (Leipzig)</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>47 069</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>KbS1suSm</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>RB Leipzig</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>88HSzjDr</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>B. Monchengladbach</t>
-        </is>
-      </c>
-      <c r="K16" t="n">
-        <v>59</v>
-      </c>
-      <c r="L16" t="n">
-        <v>591</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>UJQITUyi</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>10.11.2024 11:30</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>WWK Arena
- (Augsburg)</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>30 660</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>fTVNku3I</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Augsburg</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>hQAtP9Sl</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>Hoffenheim</t>
-        </is>
-      </c>
-      <c r="K17" t="n">
-        <v>59</v>
-      </c>
-      <c r="L17" t="n">
-        <v>591</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>UkaNveph</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>10.11.2024 13:30</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>MHPArena
- (Stuttgart)</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>60 449</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>nJQmYp1B</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>Stuttgart</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>8vndvXTk</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>Eintracht Frankfurt</t>
-        </is>
-      </c>
-      <c r="K18" t="n">
-        <v>59</v>
-      </c>
-      <c r="L18" t="n">
-        <v>591</v>
-      </c>
-      <c r="M18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>Bundesliga</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>xMovyDqH</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>10.11.2024 15:30</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Voith-Arena
- (Heidenheim)</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>15 000</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>Heidenheim</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>nwkTahLL</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>Wolfsburg</t>
-        </is>
-      </c>
-      <c r="K19" t="n">
-        <v>59</v>
-      </c>
-      <c r="L19" t="n">
-        <v>591</v>
-      </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>germany</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>

--- a/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
@@ -508,45 +508,45 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>IHYEDIog</t>
+          <t>v3DAZKP9</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>01.11.2024 16:30</t>
+          <t>08.11.2024 16:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>BayArena
- (Leverkusen)</t>
+          <t>Stadion An der Alten Försterei
+ (Berlin)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>30 210</t>
+          <t>22 012</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>4jcj2zMd</t>
+          <t>pzHW4oaE</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Bayer Leverkusen</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>nJQmYp1B</t>
+          <t>fiEQZ7C7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Stuttgart</t>
+          <t>Freiburg</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -577,45 +577,45 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>jVWMBdG5</t>
+          <t>biQrHC9r</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>02.11.2024 11:30</t>
+          <t>09.11.2024 11:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Allianz Arena
- (Munich)</t>
+          <t>Vonovia Ruhrstadion
+ (Bochum)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>75 024</t>
+          <t>26 000</t>
         </is>
       </c>
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>nVp0wiqd</t>
+          <t>8Y2m6ADe</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Bayern Munich</t>
+          <t>Bochum</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>pzHW4oaE</t>
+          <t>4jcj2zMd</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Bayer Leverkusen</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -646,45 +646,45 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>485V7EFU</t>
+          <t>nee3ysec</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>02.11.2024 11:30</t>
+          <t>09.11.2024 11:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Deutsche Bank Park
- (Frankfurt)</t>
+          <t>Mewa Arena
+ (Mainz)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>58 000</t>
+          <t>34 000</t>
         </is>
       </c>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8vndvXTk</t>
+          <t>EuakNmc1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Eintracht Frankfurt</t>
+          <t>Mainz</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>8Y2m6ADe</t>
+          <t>nP1i5US1</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Bochum</t>
+          <t>Dortmund</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -715,45 +715,45 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>8MVuSH0n</t>
+          <t>6HTjFjve</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>02.11.2024 11:30</t>
+          <t>09.11.2024 11:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>PreZero Arena
- (Sinsheim)</t>
+          <t>Millerntor-Stadion
+ (Hamburg)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>30 150</t>
+          <t>29 546</t>
         </is>
       </c>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>hQAtP9Sl</t>
+          <t>ILyJuN3g</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>St. Pauli</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>ILyJuN3g</t>
+          <t>nVp0wiqd</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>St. Pauli</t>
+          <t>Bayern Munich</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -784,45 +784,45 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2q7yHiho</t>
+          <t>YmumZjET</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>02.11.2024 11:30</t>
+          <t>09.11.2024 11:30</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Holstein-Stadion
- (Kiel)</t>
+          <t>Weserstadion
+ (Bremen)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>15 034</t>
+          <t>42 100</t>
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>63WsD2ei</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>Holstein Kiel</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>KWixEVWi</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Heidenheim</t>
         </is>
       </c>
       <c r="K6" t="n">
@@ -853,45 +853,45 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>AoSdOZaB</t>
+          <t>j5mWxZE4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>02.11.2024 11:30</t>
+          <t>09.11.2024 14:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Volkswagen Arena
- (Wolfsburg)</t>
+          <t>Red Bull Arena
+ (Leipzig)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>28 917</t>
+          <t>47 069</t>
         </is>
       </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
-          <t>nwkTahLL</t>
+          <t>KbS1suSm</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Wolfsburg</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>fTVNku3I</t>
+          <t>88HSzjDr</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Augsburg</t>
+          <t>B. Monchengladbach</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -922,45 +922,45 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>dr2N9zoI</t>
+          <t>UJQITUyi</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>02.11.2024 14:30</t>
+          <t>10.11.2024 11:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Signal Iduna Park
- (Dortmund)</t>
+          <t>WWK Arena
+ (Augsburg)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>81 365</t>
+          <t>30 660</t>
         </is>
       </c>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>nP1i5US1</t>
+          <t>fTVNku3I</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Dortmund</t>
+          <t>Augsburg</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>KbS1suSm</t>
+          <t>hQAtP9Sl</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -991,45 +991,45 @@
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>GnZmQeVb</t>
+          <t>UkaNveph</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>03.11.2024 11:30</t>
+          <t>10.11.2024 13:30</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Europa-Park Stadion
- (Freiburg)</t>
+          <t>MHPArena
+ (Stuttgart)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>34 700</t>
+          <t>60 449</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
       <c r="G9" t="inlineStr">
         <is>
-          <t>fiEQZ7C7</t>
+          <t>nJQmYp1B</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Freiburg</t>
+          <t>Stuttgart</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>EuakNmc1</t>
+          <t>8vndvXTk</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Mainz</t>
+          <t>Eintracht Frankfurt</t>
         </is>
       </c>
       <c r="K9" t="n">
@@ -1060,45 +1060,45 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>raQ4MDUN</t>
+          <t>xMovyDqH</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>03.11.2024 13:30</t>
+          <t>10.11.2024 15:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Borussia-Park
- (Mönchengladbach)</t>
+          <t>Voith-Arena
+ (Heidenheim)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>54 042</t>
+          <t>15 000</t>
         </is>
       </c>
       <c r="F10" t="inlineStr"/>
       <c r="G10" t="inlineStr">
         <is>
-          <t>88HSzjDr</t>
+          <t>KWixEVWi</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>B. Monchengladbach</t>
+          <t>Heidenheim</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Ig1f1fy3</t>
+          <t>nwkTahLL</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Werder Bremen</t>
+          <t>Wolfsburg</t>
         </is>
       </c>
       <c r="K10" t="n">

--- a/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
+++ b/data/germany/p6_deployment/data_understanding/df_match_next.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:T17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,30 +476,50 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
           <t>id_country</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>id_competition</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>is_cup</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>season</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>country</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>competition</t>
         </is>
@@ -516,7 +536,12 @@
           <t>08.11.2024 16:30</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Reichel T.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>Stadion An der Alten Försterei
@@ -549,26 +574,46 @@
           <t>Freiburg</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>hpYJ6izc</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>svensson bo</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>YZPE6Sx7</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>schuster julian</t>
+        </is>
+      </c>
+      <c r="O2" t="n">
         <v>59</v>
       </c>
-      <c r="L2" t="n">
+      <c r="P2" t="n">
         <v>591</v>
       </c>
-      <c r="M2" t="n">
+      <c r="Q2" t="n">
         <v>0</v>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="T2" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
@@ -585,7 +630,12 @@
           <t>09.11.2024 11:30</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Hartmann R.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D3" t="inlineStr">
         <is>
           <t>Vonovia Ruhrstadion
@@ -618,26 +668,30 @@
           <t>Bayer Leverkusen</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="n">
         <v>59</v>
       </c>
-      <c r="L3" t="n">
+      <c r="P3" t="n">
         <v>591</v>
       </c>
-      <c r="M3" t="n">
+      <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="R3" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="T3" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
@@ -654,7 +708,12 @@
           <t>09.11.2024 11:30</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Badstubner F.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D4" t="inlineStr">
         <is>
           <t>Mewa Arena
@@ -687,26 +746,30 @@
           <t>Dortmund</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="n">
         <v>59</v>
       </c>
-      <c r="L4" t="n">
+      <c r="P4" t="n">
         <v>591</v>
       </c>
-      <c r="M4" t="n">
+      <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="R4" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr">
+      <c r="T4" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
@@ -723,7 +786,12 @@
           <t>09.11.2024 11:30</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Gerach T.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D5" t="inlineStr">
         <is>
           <t>Millerntor-Stadion
@@ -756,26 +824,30 @@
           <t>Bayern Munich</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="n">
         <v>59</v>
       </c>
-      <c r="L5" t="n">
+      <c r="P5" t="n">
         <v>591</v>
       </c>
-      <c r="M5" t="n">
+      <c r="Q5" t="n">
         <v>0</v>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
@@ -792,7 +864,12 @@
           <t>09.11.2024 11:30</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Storks S.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D6" t="inlineStr">
         <is>
           <t>Weserstadion
@@ -825,26 +902,30 @@
           <t>Holstein Kiel</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="n">
         <v>59</v>
       </c>
-      <c r="L6" t="n">
+      <c r="P6" t="n">
         <v>591</v>
       </c>
-      <c r="M6" t="n">
+      <c r="Q6" t="n">
         <v>0</v>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="R6" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr">
+      <c r="T6" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
@@ -861,7 +942,12 @@
           <t>09.11.2024 14:30</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Dingert C.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr">
         <is>
           <t>Red Bull Arena
@@ -894,26 +980,30 @@
           <t>B. Monchengladbach</t>
         </is>
       </c>
-      <c r="K7" t="n">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="n">
         <v>59</v>
       </c>
-      <c r="L7" t="n">
+      <c r="P7" t="n">
         <v>591</v>
       </c>
-      <c r="M7" t="n">
+      <c r="Q7" t="n">
         <v>0</v>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="R7" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr">
+      <c r="T7" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
@@ -963,26 +1053,30 @@
           <t>Hoffenheim</t>
         </is>
       </c>
-      <c r="K8" t="n">
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="n">
         <v>59</v>
       </c>
-      <c r="L8" t="n">
+      <c r="P8" t="n">
         <v>591</v>
       </c>
-      <c r="M8" t="n">
+      <c r="Q8" t="n">
         <v>0</v>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="T8" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
@@ -999,7 +1093,12 @@
           <t>10.11.2024 13:30</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Zwayer F.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D9" t="inlineStr">
         <is>
           <t>MHPArena
@@ -1032,26 +1131,30 @@
           <t>Eintracht Frankfurt</t>
         </is>
       </c>
-      <c r="K9" t="n">
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="n">
         <v>59</v>
       </c>
-      <c r="L9" t="n">
+      <c r="P9" t="n">
         <v>591</v>
       </c>
-      <c r="M9" t="n">
+      <c r="Q9" t="n">
         <v>0</v>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="R9" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr">
+      <c r="T9" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
@@ -1068,7 +1171,12 @@
           <t>10.11.2024 15:30</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Osmers H.
+ (Ger)</t>
+        </is>
+      </c>
       <c r="D10" t="inlineStr">
         <is>
           <t>Voith-Arena
@@ -1101,26 +1209,541 @@
           <t>Wolfsburg</t>
         </is>
       </c>
-      <c r="K10" t="n">
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="n">
         <v>59</v>
       </c>
-      <c r="L10" t="n">
+      <c r="P10" t="n">
         <v>591</v>
       </c>
-      <c r="M10" t="n">
+      <c r="Q10" t="n">
         <v>0</v>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>germany</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr">
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>EuQnZBVQ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>22.11.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Allianz Arena
+ (Munich)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>75 024</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>nVp0wiqd</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Bayern Munich</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>fTVNku3I</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="n">
+        <v>59</v>
+      </c>
+      <c r="P11" t="n">
+        <v>591</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2qNaDU87</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>23.11.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>BayArena
+ (Leverkusen)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>30 210</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>4jcj2zMd</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>Bayer Leverkusen</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>KWixEVWi</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Heidenheim</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="n">
+        <v>59</v>
+      </c>
+      <c r="P12" t="n">
+        <v>591</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pOGITkgl</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>23.11.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Signal Iduna Park
+ (Dortmund)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>81 365</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>nP1i5US1</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>fiEQZ7C7</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Freiburg</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="n">
+        <v>59</v>
+      </c>
+      <c r="P13" t="n">
+        <v>591</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>0</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>E38ZP7hD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>23.11.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>PreZero Arena
+ (Sinsheim)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>30 150</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>hQAtP9Sl</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Hoffenheim</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>KbS1suSm</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>RB Leipzig</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="n">
+        <v>59</v>
+      </c>
+      <c r="P14" t="n">
+        <v>591</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>fwAoyY0E</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>23.11.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>MHPArena
+ (Stuttgart)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>60 449</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>nJQmYp1B</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Stuttgart</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>8Y2m6ADe</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Bochum</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="n">
+        <v>59</v>
+      </c>
+      <c r="P15" t="n">
+        <v>591</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SrjMmBpK</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>23.11.2024 11:30</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Volkswagen Arena
+ (Wolfsburg)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>28 917</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>nwkTahLL</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Wolfsburg</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>pzHW4oaE</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Union Berlin</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="n">
+        <v>59</v>
+      </c>
+      <c r="P16" t="n">
+        <v>591</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Bundesliga</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>6w5RRTN0</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>23.11.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Deutsche Bank Park
+ (Frankfurt)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>58 000</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>8vndvXTk</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Eintracht Frankfurt</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Ig1f1fy3</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Werder Bremen</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="n">
+        <v>59</v>
+      </c>
+      <c r="P17" t="n">
+        <v>591</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>germany</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
         <is>
           <t>Bundesliga</t>
         </is>
